--- a/giolbas.xlsx
+++ b/giolbas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b71db5f754a3740e/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2923" documentId="8_{0173481B-EB28-4B1F-8AE6-5D1A837885A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B38E6193-CD37-41C2-9671-FAFB4402CE88}"/>
+  <xr:revisionPtr revIDLastSave="2127" documentId="13_ncr:1_{FAF98411-C9F4-4531-8DBB-D639F62302C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6A606A5-6AB9-45EE-8086-8B8CFB7F7154}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{95818898-689F-4175-9487-A303FD0FABB6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{95818898-689F-4175-9487-A303FD0FABB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="315">
   <si>
     <t>informe_id</t>
   </si>
@@ -974,12 +974,33 @@
   <si>
     <t>LEVANTAR MAS MURO</t>
   </si>
+  <si>
+    <t>SIN REJILLA</t>
+  </si>
+  <si>
+    <t>INS0</t>
+  </si>
+  <si>
+    <t>NO TIENE 2 DE 10"</t>
+  </si>
+  <si>
+    <t>EVAUAR</t>
+  </si>
+  <si>
+    <t>CAMBIAR TUBOS</t>
+  </si>
+  <si>
+    <t>LE FALTA UNA DE 6"</t>
+  </si>
+  <si>
+    <t>INOPERATIVA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1001,8 +1022,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1012,6 +1040,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1028,12 +1074,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1371,7 +1421,9 @@
   <dimension ref="A1:DW63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="11.42578125" customWidth="1"/>
+    <col min="1" max="6" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -1904,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="AX2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY2">
         <v>0</v>
@@ -1955,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP2">
         <v>0</v>
@@ -2004,7 +2056,7 @@
       </c>
       <c r="CE2">
         <f>SUM(AV2:CD2)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CF2">
         <v>0</v>
@@ -2019,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="CT2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU2">
         <v>0</v>
@@ -2028,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="CW2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX2">
         <v>0</v>
@@ -2074,7 +2126,7 @@
       </c>
       <c r="DL2">
         <f>SUM(CQ2:DK2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="s">
         <v>265</v>
@@ -2412,9 +2464,6 @@
       <c r="N4" t="s">
         <v>88</v>
       </c>
-      <c r="O4" t="s">
-        <v>88</v>
-      </c>
       <c r="P4" t="s">
         <v>89</v>
       </c>
@@ -2943,11 +2992,8 @@
       <c r="DT5">
         <v>15.2</v>
       </c>
-      <c r="DU5" s="2">
+      <c r="DV5">
         <v>5</v>
-      </c>
-      <c r="DV5">
-        <v>5.2</v>
       </c>
       <c r="DW5">
         <v>5.2</v>
@@ -5782,7 +5828,7 @@
         <v>278</v>
       </c>
       <c r="AC16" t="s">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="AF16" t="s">
         <v>273</v>
@@ -8051,7 +8097,7 @@
         <v>225</v>
       </c>
       <c r="AC24" t="s">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="AL24" t="s">
         <v>273</v>
@@ -8279,7 +8325,7 @@
       <c r="H25" t="s">
         <v>116</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="4">
         <v>7343581</v>
       </c>
       <c r="J25" t="s">
@@ -9477,7 +9523,7 @@
         <v>225</v>
       </c>
       <c r="AC30" t="s">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="AF30" t="s">
         <v>273</v>
@@ -9765,7 +9811,7 @@
         <v>301</v>
       </c>
       <c r="AC31" t="s">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="AP31" t="s">
         <v>226</v>
@@ -10047,7 +10093,7 @@
         <v>225</v>
       </c>
       <c r="AC32" t="s">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="AF32" t="s">
         <v>273</v>
@@ -10329,7 +10375,7 @@
         <v>225</v>
       </c>
       <c r="AC33" t="s">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="AF33" t="s">
         <v>273</v>
@@ -10686,16 +10732,145 @@
       <c r="BM34">
         <v>1</v>
       </c>
+      <c r="BN34">
+        <v>0</v>
+      </c>
+      <c r="BO34">
+        <v>0</v>
+      </c>
+      <c r="BP34">
+        <v>0</v>
+      </c>
+      <c r="BQ34">
+        <v>0</v>
+      </c>
+      <c r="BR34">
+        <v>0</v>
+      </c>
+      <c r="BS34">
+        <v>0</v>
+      </c>
+      <c r="BT34">
+        <v>1</v>
+      </c>
+      <c r="BU34">
+        <v>0</v>
+      </c>
+      <c r="BV34">
+        <v>0</v>
+      </c>
+      <c r="BW34">
+        <v>0</v>
+      </c>
+      <c r="BX34">
+        <v>0</v>
+      </c>
+      <c r="BY34">
+        <v>0</v>
+      </c>
+      <c r="BZ34">
+        <v>0</v>
+      </c>
+      <c r="CA34">
+        <v>0</v>
+      </c>
+      <c r="CB34">
+        <v>1</v>
+      </c>
+      <c r="CC34">
+        <v>0</v>
+      </c>
+      <c r="CD34">
+        <v>0</v>
+      </c>
       <c r="CE34">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CF34">
+        <v>0</v>
+      </c>
+      <c r="CQ34">
+        <v>0</v>
+      </c>
+      <c r="CR34">
+        <v>0</v>
+      </c>
+      <c r="CS34">
+        <v>0</v>
+      </c>
+      <c r="CT34">
+        <v>0</v>
+      </c>
+      <c r="CU34">
+        <v>0</v>
+      </c>
+      <c r="CV34">
+        <v>0</v>
+      </c>
+      <c r="CW34">
+        <v>0</v>
+      </c>
+      <c r="CX34">
+        <v>0</v>
+      </c>
+      <c r="CY34">
+        <v>0</v>
+      </c>
+      <c r="CZ34">
+        <v>0</v>
+      </c>
+      <c r="DA34">
+        <v>0</v>
+      </c>
+      <c r="DB34">
+        <v>0</v>
+      </c>
+      <c r="DC34">
+        <v>0</v>
+      </c>
+      <c r="DD34">
+        <v>0</v>
+      </c>
+      <c r="DE34">
+        <v>0</v>
+      </c>
+      <c r="DF34">
+        <v>0</v>
+      </c>
+      <c r="DG34">
+        <v>0</v>
+      </c>
+      <c r="DH34">
+        <v>0</v>
+      </c>
+      <c r="DI34">
+        <v>0</v>
+      </c>
+      <c r="DJ34">
+        <v>0</v>
+      </c>
+      <c r="DK34">
         <v>0</v>
       </c>
       <c r="DL34">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="DN34" t="s">
+        <v>276</v>
+      </c>
+      <c r="DO34" t="s">
+        <v>224</v>
+      </c>
+      <c r="DT34">
+        <v>11</v>
+      </c>
+      <c r="DV34">
+        <v>4</v>
+      </c>
+      <c r="DW34">
+        <v>4.2</v>
       </c>
     </row>
     <row r="35" spans="1:127" x14ac:dyDescent="0.25">
@@ -10732,16 +10907,235 @@
       <c r="K35">
         <v>350</v>
       </c>
+      <c r="L35" t="s">
+        <v>88</v>
+      </c>
+      <c r="M35" t="s">
+        <v>88</v>
+      </c>
+      <c r="N35" t="s">
+        <v>89</v>
+      </c>
+      <c r="O35" t="s">
+        <v>88</v>
+      </c>
+      <c r="P35" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>88</v>
+      </c>
+      <c r="R35" t="s">
+        <v>88</v>
+      </c>
+      <c r="S35" t="s">
+        <v>88</v>
+      </c>
+      <c r="T35" t="s">
+        <v>88</v>
+      </c>
+      <c r="U35" t="s">
+        <v>88</v>
+      </c>
+      <c r="V35" t="s">
+        <v>88</v>
+      </c>
+      <c r="W35" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV35">
+        <v>0</v>
+      </c>
+      <c r="AW35">
+        <v>0</v>
+      </c>
+      <c r="AX35">
+        <v>0</v>
+      </c>
+      <c r="AY35">
+        <v>1</v>
+      </c>
+      <c r="AZ35">
+        <v>0</v>
+      </c>
+      <c r="BA35">
+        <v>0</v>
+      </c>
+      <c r="BB35">
+        <v>0</v>
+      </c>
+      <c r="BC35">
+        <v>0</v>
+      </c>
+      <c r="BD35">
+        <v>0</v>
+      </c>
+      <c r="BE35">
+        <v>2</v>
+      </c>
+      <c r="BF35">
+        <v>0</v>
+      </c>
+      <c r="BG35">
+        <v>0</v>
+      </c>
+      <c r="BH35">
+        <v>0</v>
+      </c>
+      <c r="BI35">
+        <v>0</v>
+      </c>
+      <c r="BJ35">
+        <v>0</v>
+      </c>
+      <c r="BK35">
+        <v>0</v>
+      </c>
+      <c r="BL35">
+        <v>0</v>
+      </c>
+      <c r="BM35">
+        <v>1</v>
+      </c>
+      <c r="BN35">
+        <v>0</v>
+      </c>
+      <c r="BO35">
+        <v>0</v>
+      </c>
+      <c r="BP35">
+        <v>0</v>
+      </c>
+      <c r="BQ35">
+        <v>0</v>
+      </c>
+      <c r="BR35">
+        <v>0</v>
+      </c>
+      <c r="BS35">
+        <v>0</v>
+      </c>
+      <c r="BT35">
+        <v>1</v>
+      </c>
+      <c r="BU35">
+        <v>0</v>
+      </c>
+      <c r="BV35">
+        <v>0</v>
+      </c>
+      <c r="BW35">
+        <v>0</v>
+      </c>
+      <c r="BX35">
+        <v>0</v>
+      </c>
+      <c r="BY35">
+        <v>0</v>
+      </c>
+      <c r="BZ35">
+        <v>0</v>
+      </c>
+      <c r="CA35">
+        <v>0</v>
+      </c>
+      <c r="CB35">
+        <v>1</v>
+      </c>
+      <c r="CC35">
+        <v>0</v>
+      </c>
+      <c r="CD35">
+        <v>0</v>
+      </c>
       <c r="CE35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF35">
+        <v>0</v>
+      </c>
+      <c r="CQ35">
+        <v>0</v>
+      </c>
+      <c r="CR35">
+        <v>0</v>
+      </c>
+      <c r="CS35">
+        <v>0</v>
+      </c>
+      <c r="CT35">
+        <v>1</v>
+      </c>
+      <c r="CU35">
+        <v>0</v>
+      </c>
+      <c r="CV35">
+        <v>0</v>
+      </c>
+      <c r="CW35">
+        <v>0</v>
+      </c>
+      <c r="CX35">
+        <v>0</v>
+      </c>
+      <c r="CY35">
+        <v>0</v>
+      </c>
+      <c r="CZ35">
+        <v>1</v>
+      </c>
+      <c r="DA35">
+        <v>0</v>
+      </c>
+      <c r="DB35">
+        <v>0</v>
+      </c>
+      <c r="DC35">
+        <v>0</v>
+      </c>
+      <c r="DD35">
+        <v>0</v>
+      </c>
+      <c r="DE35">
+        <v>0</v>
+      </c>
+      <c r="DF35">
+        <v>0</v>
+      </c>
+      <c r="DG35">
+        <v>0</v>
+      </c>
+      <c r="DH35">
+        <v>0</v>
+      </c>
+      <c r="DI35">
+        <v>0</v>
+      </c>
+      <c r="DJ35">
+        <v>0</v>
+      </c>
+      <c r="DK35">
         <v>0</v>
       </c>
       <c r="DL35">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="DT35">
+        <v>9.9</v>
+      </c>
+      <c r="DV35">
+        <v>4.8</v>
+      </c>
+      <c r="DW35">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:127" x14ac:dyDescent="0.25">
@@ -10778,16 +11172,241 @@
       <c r="K36">
         <v>1750</v>
       </c>
+      <c r="L36" t="s">
+        <v>88</v>
+      </c>
+      <c r="M36" t="s">
+        <v>88</v>
+      </c>
+      <c r="N36" t="s">
+        <v>89</v>
+      </c>
+      <c r="O36" t="s">
+        <v>88</v>
+      </c>
+      <c r="P36" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>88</v>
+      </c>
+      <c r="R36" t="s">
+        <v>88</v>
+      </c>
+      <c r="S36" t="s">
+        <v>88</v>
+      </c>
+      <c r="T36" t="s">
+        <v>88</v>
+      </c>
+      <c r="U36" t="s">
+        <v>88</v>
+      </c>
+      <c r="V36" t="s">
+        <v>88</v>
+      </c>
+      <c r="W36" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>278</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV36">
+        <v>0</v>
+      </c>
+      <c r="AW36">
+        <v>0</v>
+      </c>
+      <c r="AX36">
+        <v>0</v>
+      </c>
+      <c r="AY36">
+        <v>0</v>
+      </c>
+      <c r="AZ36">
+        <v>0</v>
+      </c>
+      <c r="BA36">
+        <v>0</v>
+      </c>
+      <c r="BB36" s="2">
+        <v>1</v>
+      </c>
+      <c r="BC36">
+        <v>0</v>
+      </c>
+      <c r="BD36">
+        <v>0</v>
+      </c>
+      <c r="BE36">
+        <v>0</v>
+      </c>
+      <c r="BF36">
+        <v>0</v>
+      </c>
+      <c r="BG36">
+        <v>0</v>
+      </c>
+      <c r="BH36">
+        <v>0</v>
+      </c>
+      <c r="BI36">
+        <v>0</v>
+      </c>
+      <c r="BJ36">
+        <v>0</v>
+      </c>
+      <c r="BK36">
+        <v>0</v>
+      </c>
+      <c r="BL36">
+        <v>0</v>
+      </c>
+      <c r="BM36">
+        <v>0</v>
+      </c>
+      <c r="BN36">
+        <v>0</v>
+      </c>
+      <c r="BO36">
+        <v>0</v>
+      </c>
+      <c r="BP36" s="2">
+        <v>1</v>
+      </c>
+      <c r="BQ36">
+        <v>0</v>
+      </c>
+      <c r="BR36">
+        <v>0</v>
+      </c>
+      <c r="BS36">
+        <v>0</v>
+      </c>
+      <c r="BT36">
+        <v>0</v>
+      </c>
+      <c r="BU36">
+        <v>0</v>
+      </c>
+      <c r="BV36">
+        <v>0</v>
+      </c>
+      <c r="BW36" s="2">
+        <v>1</v>
+      </c>
+      <c r="BX36">
+        <v>0</v>
+      </c>
+      <c r="BY36">
+        <v>0</v>
+      </c>
+      <c r="BZ36">
+        <v>0</v>
+      </c>
+      <c r="CA36">
+        <v>0</v>
+      </c>
+      <c r="CB36">
+        <v>0</v>
+      </c>
+      <c r="CC36">
+        <v>0</v>
+      </c>
+      <c r="CD36" s="2">
+        <v>1</v>
+      </c>
       <c r="CE36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CF36">
+        <v>0</v>
+      </c>
+      <c r="CQ36">
+        <v>0</v>
+      </c>
+      <c r="CR36">
+        <v>0</v>
+      </c>
+      <c r="CS36">
+        <v>0</v>
+      </c>
+      <c r="CT36">
+        <v>0</v>
+      </c>
+      <c r="CU36">
+        <v>0</v>
+      </c>
+      <c r="CV36">
+        <v>0</v>
+      </c>
+      <c r="CW36">
+        <v>1</v>
+      </c>
+      <c r="CX36">
+        <v>0</v>
+      </c>
+      <c r="CY36">
+        <v>0</v>
+      </c>
+      <c r="CZ36">
+        <v>0</v>
+      </c>
+      <c r="DA36">
+        <v>0</v>
+      </c>
+      <c r="DB36">
+        <v>0</v>
+      </c>
+      <c r="DC36">
+        <v>0</v>
+      </c>
+      <c r="DD36">
+        <v>0</v>
+      </c>
+      <c r="DE36">
+        <v>0</v>
+      </c>
+      <c r="DF36">
+        <v>0</v>
+      </c>
+      <c r="DG36">
+        <v>0</v>
+      </c>
+      <c r="DH36">
+        <v>0</v>
+      </c>
+      <c r="DI36">
+        <v>0</v>
+      </c>
+      <c r="DJ36">
+        <v>0</v>
+      </c>
+      <c r="DK36">
         <v>0</v>
       </c>
       <c r="DL36">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DP36" t="s">
+        <v>283</v>
+      </c>
+      <c r="DQ36" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT36">
+        <v>16.8</v>
+      </c>
+      <c r="DV36">
+        <v>8</v>
+      </c>
+      <c r="DW36">
+        <v>8.4</v>
       </c>
     </row>
     <row r="37" spans="1:127" x14ac:dyDescent="0.25">
@@ -10824,16 +11443,228 @@
       <c r="K37">
         <v>1200</v>
       </c>
+      <c r="L37" t="s">
+        <v>88</v>
+      </c>
+      <c r="M37" t="s">
+        <v>88</v>
+      </c>
+      <c r="N37" t="s">
+        <v>88</v>
+      </c>
+      <c r="O37" t="s">
+        <v>88</v>
+      </c>
+      <c r="P37" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>88</v>
+      </c>
+      <c r="R37" t="s">
+        <v>88</v>
+      </c>
+      <c r="S37" t="s">
+        <v>88</v>
+      </c>
+      <c r="T37" t="s">
+        <v>88</v>
+      </c>
+      <c r="U37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V37" t="s">
+        <v>88</v>
+      </c>
+      <c r="W37" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV37">
+        <v>0</v>
+      </c>
+      <c r="AW37">
+        <v>0</v>
+      </c>
+      <c r="AX37">
+        <v>0</v>
+      </c>
+      <c r="AY37">
+        <v>0</v>
+      </c>
+      <c r="AZ37">
+        <v>0</v>
+      </c>
+      <c r="BA37">
+        <v>0</v>
+      </c>
+      <c r="BB37">
+        <v>1</v>
+      </c>
+      <c r="BC37">
+        <v>0</v>
+      </c>
+      <c r="BD37">
+        <v>0</v>
+      </c>
+      <c r="BE37">
+        <v>0</v>
+      </c>
+      <c r="BF37">
+        <v>2</v>
+      </c>
+      <c r="BG37">
+        <v>0</v>
+      </c>
+      <c r="BH37">
+        <v>0</v>
+      </c>
+      <c r="BI37">
+        <v>0</v>
+      </c>
+      <c r="BJ37">
+        <v>0</v>
+      </c>
+      <c r="BK37">
+        <v>0</v>
+      </c>
+      <c r="BL37">
+        <v>0</v>
+      </c>
+      <c r="BM37">
+        <v>0</v>
+      </c>
+      <c r="BN37">
+        <v>0</v>
+      </c>
+      <c r="BO37">
+        <v>0</v>
+      </c>
+      <c r="BP37">
+        <v>1</v>
+      </c>
+      <c r="BQ37">
+        <v>0</v>
+      </c>
+      <c r="BR37">
+        <v>0</v>
+      </c>
+      <c r="BS37">
+        <v>0</v>
+      </c>
+      <c r="BT37">
+        <v>0</v>
+      </c>
+      <c r="BU37">
+        <v>0</v>
+      </c>
+      <c r="BV37">
+        <v>0</v>
+      </c>
+      <c r="BW37">
+        <v>1</v>
+      </c>
+      <c r="BX37">
+        <v>0</v>
+      </c>
+      <c r="BY37">
+        <v>0</v>
+      </c>
+      <c r="BZ37">
+        <v>0</v>
+      </c>
+      <c r="CA37">
+        <v>0</v>
+      </c>
+      <c r="CB37">
+        <v>0</v>
+      </c>
+      <c r="CC37">
+        <v>1</v>
+      </c>
+      <c r="CD37">
+        <v>0</v>
+      </c>
       <c r="CE37">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CF37">
+        <v>6</v>
+      </c>
+      <c r="CQ37">
+        <v>0</v>
+      </c>
+      <c r="CR37">
+        <v>0</v>
+      </c>
+      <c r="CS37">
+        <v>0</v>
+      </c>
+      <c r="CT37">
+        <v>0</v>
+      </c>
+      <c r="CU37">
+        <v>0</v>
+      </c>
+      <c r="CV37">
+        <v>0</v>
+      </c>
+      <c r="CW37" s="3">
+        <v>1</v>
+      </c>
+      <c r="CX37">
+        <v>0</v>
+      </c>
+      <c r="CY37">
+        <v>0</v>
+      </c>
+      <c r="CZ37">
+        <v>0</v>
+      </c>
+      <c r="DA37">
+        <v>0</v>
+      </c>
+      <c r="DB37">
+        <v>0</v>
+      </c>
+      <c r="DC37">
+        <v>0</v>
+      </c>
+      <c r="DD37" s="3">
+        <v>1</v>
+      </c>
+      <c r="DE37">
+        <v>0</v>
+      </c>
+      <c r="DF37">
+        <v>0</v>
+      </c>
+      <c r="DG37">
+        <v>0</v>
+      </c>
+      <c r="DH37">
+        <v>0</v>
+      </c>
+      <c r="DI37">
+        <v>0</v>
+      </c>
+      <c r="DJ37">
+        <v>0</v>
+      </c>
+      <c r="DK37">
         <v>0</v>
       </c>
       <c r="DL37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="DT37">
+        <v>15</v>
+      </c>
+      <c r="DV37">
+        <v>6</v>
+      </c>
+      <c r="DW37">
+        <v>6.4</v>
       </c>
     </row>
     <row r="38" spans="1:127" x14ac:dyDescent="0.25">
@@ -10870,16 +11701,232 @@
       <c r="K38">
         <v>100</v>
       </c>
+      <c r="L38" t="s">
+        <v>88</v>
+      </c>
+      <c r="M38" t="s">
+        <v>88</v>
+      </c>
+      <c r="N38" t="s">
+        <v>88</v>
+      </c>
+      <c r="O38" t="s">
+        <v>88</v>
+      </c>
+      <c r="P38" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>88</v>
+      </c>
+      <c r="R38" t="s">
+        <v>88</v>
+      </c>
+      <c r="S38" t="s">
+        <v>88</v>
+      </c>
+      <c r="T38" t="s">
+        <v>88</v>
+      </c>
+      <c r="U38" t="s">
+        <v>88</v>
+      </c>
+      <c r="V38" t="s">
+        <v>88</v>
+      </c>
+      <c r="W38" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV38">
+        <v>0</v>
+      </c>
+      <c r="AW38">
+        <v>0</v>
+      </c>
+      <c r="AX38">
+        <v>1</v>
+      </c>
+      <c r="AY38">
+        <v>0</v>
+      </c>
+      <c r="AZ38">
+        <v>0</v>
+      </c>
+      <c r="BA38">
+        <v>0</v>
+      </c>
+      <c r="BB38">
+        <v>0</v>
+      </c>
+      <c r="BC38">
+        <v>0</v>
+      </c>
+      <c r="BD38">
+        <v>0</v>
+      </c>
+      <c r="BE38">
+        <v>0</v>
+      </c>
+      <c r="BF38">
+        <v>0</v>
+      </c>
+      <c r="BG38">
+        <v>0</v>
+      </c>
+      <c r="BH38">
+        <v>0</v>
+      </c>
+      <c r="BI38">
+        <v>0</v>
+      </c>
+      <c r="BJ38">
+        <v>0</v>
+      </c>
+      <c r="BK38">
+        <v>0</v>
+      </c>
+      <c r="BL38">
+        <v>1</v>
+      </c>
+      <c r="BM38">
+        <v>0</v>
+      </c>
+      <c r="BN38">
+        <v>0</v>
+      </c>
+      <c r="BO38">
+        <v>0</v>
+      </c>
+      <c r="BP38">
+        <v>0</v>
+      </c>
+      <c r="BQ38">
+        <v>0</v>
+      </c>
+      <c r="BR38">
+        <v>0</v>
+      </c>
+      <c r="BS38">
+        <v>1</v>
+      </c>
+      <c r="BT38">
+        <v>0</v>
+      </c>
+      <c r="BU38">
+        <v>0</v>
+      </c>
+      <c r="BV38">
+        <v>0</v>
+      </c>
+      <c r="BW38">
+        <v>0</v>
+      </c>
+      <c r="BX38">
+        <v>0</v>
+      </c>
+      <c r="BY38">
+        <v>0</v>
+      </c>
+      <c r="BZ38">
+        <v>0</v>
+      </c>
+      <c r="CA38">
+        <v>1</v>
+      </c>
+      <c r="CB38">
+        <v>0</v>
+      </c>
+      <c r="CC38">
+        <v>0</v>
+      </c>
+      <c r="CD38">
+        <v>0</v>
+      </c>
       <c r="CE38">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CF38">
+        <v>0</v>
+      </c>
+      <c r="CQ38">
+        <v>0</v>
+      </c>
+      <c r="CR38">
+        <v>0</v>
+      </c>
+      <c r="CS38">
+        <v>1</v>
+      </c>
+      <c r="CT38">
+        <v>0</v>
+      </c>
+      <c r="CU38">
+        <v>0</v>
+      </c>
+      <c r="CV38">
+        <v>0</v>
+      </c>
+      <c r="CW38">
+        <v>0</v>
+      </c>
+      <c r="CX38">
+        <v>0</v>
+      </c>
+      <c r="CY38">
+        <v>0</v>
+      </c>
+      <c r="CZ38">
+        <v>0</v>
+      </c>
+      <c r="DA38">
+        <v>0</v>
+      </c>
+      <c r="DB38">
+        <v>0</v>
+      </c>
+      <c r="DC38">
+        <v>0</v>
+      </c>
+      <c r="DD38">
+        <v>0</v>
+      </c>
+      <c r="DE38">
+        <v>0</v>
+      </c>
+      <c r="DF38">
+        <v>0</v>
+      </c>
+      <c r="DG38">
+        <v>0</v>
+      </c>
+      <c r="DH38">
+        <v>0</v>
+      </c>
+      <c r="DI38">
+        <v>0</v>
+      </c>
+      <c r="DJ38">
+        <v>0</v>
+      </c>
+      <c r="DK38">
         <v>0</v>
       </c>
       <c r="DL38">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DT38" s="2">
+        <v>5</v>
+      </c>
+      <c r="DU38" s="2">
+        <v>5</v>
+      </c>
+      <c r="DV38" s="2">
+        <v>4</v>
+      </c>
+      <c r="DW38" s="2">
+        <v>4.5</v>
       </c>
     </row>
     <row r="39" spans="1:127" x14ac:dyDescent="0.25">
@@ -10916,16 +11963,241 @@
       <c r="K39">
         <v>300</v>
       </c>
+      <c r="L39" t="s">
+        <v>88</v>
+      </c>
+      <c r="M39" t="s">
+        <v>88</v>
+      </c>
+      <c r="N39" t="s">
+        <v>88</v>
+      </c>
+      <c r="O39" t="s">
+        <v>88</v>
+      </c>
+      <c r="P39" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>88</v>
+      </c>
+      <c r="R39" t="s">
+        <v>88</v>
+      </c>
+      <c r="S39" t="s">
+        <v>88</v>
+      </c>
+      <c r="T39" t="s">
+        <v>88</v>
+      </c>
+      <c r="U39" t="s">
+        <v>88</v>
+      </c>
+      <c r="V39" t="s">
+        <v>88</v>
+      </c>
+      <c r="W39" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV39">
+        <v>0</v>
+      </c>
+      <c r="AW39">
+        <v>0</v>
+      </c>
+      <c r="AX39">
+        <v>0</v>
+      </c>
+      <c r="AY39">
+        <v>1</v>
+      </c>
+      <c r="AZ39">
+        <v>0</v>
+      </c>
+      <c r="BA39">
+        <v>0</v>
+      </c>
+      <c r="BB39">
+        <v>0</v>
+      </c>
+      <c r="BC39">
+        <v>0</v>
+      </c>
+      <c r="BD39">
+        <v>0</v>
+      </c>
+      <c r="BE39">
+        <v>3</v>
+      </c>
+      <c r="BF39">
+        <v>0</v>
+      </c>
+      <c r="BG39">
+        <v>0</v>
+      </c>
+      <c r="BH39">
+        <v>0</v>
+      </c>
+      <c r="BI39">
+        <v>0</v>
+      </c>
+      <c r="BJ39">
+        <v>0</v>
+      </c>
+      <c r="BK39">
+        <v>0</v>
+      </c>
+      <c r="BL39">
+        <v>1</v>
+      </c>
+      <c r="BM39">
+        <v>0</v>
+      </c>
+      <c r="BN39">
+        <v>0</v>
+      </c>
+      <c r="BO39">
+        <v>0</v>
+      </c>
+      <c r="BP39">
+        <v>0</v>
+      </c>
+      <c r="BQ39">
+        <v>0</v>
+      </c>
+      <c r="BR39">
+        <v>0</v>
+      </c>
+      <c r="BS39">
+        <v>1</v>
+      </c>
+      <c r="BT39">
+        <v>0</v>
+      </c>
+      <c r="BU39">
+        <v>0</v>
+      </c>
+      <c r="BV39">
+        <v>0</v>
+      </c>
+      <c r="BW39">
+        <v>0</v>
+      </c>
+      <c r="BX39">
+        <v>0</v>
+      </c>
+      <c r="BY39">
+        <v>0</v>
+      </c>
+      <c r="BZ39">
+        <v>0</v>
+      </c>
+      <c r="CA39">
+        <v>0</v>
+      </c>
+      <c r="CB39">
+        <v>1</v>
+      </c>
+      <c r="CC39">
+        <v>0</v>
+      </c>
+      <c r="CD39">
+        <v>0</v>
+      </c>
       <c r="CE39">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CF39">
+        <v>0</v>
+      </c>
+      <c r="CQ39">
+        <v>0</v>
+      </c>
+      <c r="CR39">
+        <v>0</v>
+      </c>
+      <c r="CS39">
+        <v>0</v>
+      </c>
+      <c r="CT39">
+        <v>0</v>
+      </c>
+      <c r="CU39">
+        <v>0</v>
+      </c>
+      <c r="CV39">
+        <v>0</v>
+      </c>
+      <c r="CW39">
+        <v>0</v>
+      </c>
+      <c r="CX39">
+        <v>0</v>
+      </c>
+      <c r="CY39">
+        <v>0</v>
+      </c>
+      <c r="CZ39">
+        <v>0</v>
+      </c>
+      <c r="DA39">
+        <v>0</v>
+      </c>
+      <c r="DB39">
+        <v>0</v>
+      </c>
+      <c r="DC39">
+        <v>0</v>
+      </c>
+      <c r="DD39">
+        <v>0</v>
+      </c>
+      <c r="DE39">
+        <v>0</v>
+      </c>
+      <c r="DF39">
+        <v>0</v>
+      </c>
+      <c r="DG39">
+        <v>0</v>
+      </c>
+      <c r="DH39">
+        <v>0</v>
+      </c>
+      <c r="DI39">
+        <v>0</v>
+      </c>
+      <c r="DJ39">
+        <v>0</v>
+      </c>
+      <c r="DK39">
         <v>0</v>
       </c>
       <c r="DL39">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="DN39" t="s">
+        <v>277</v>
+      </c>
+      <c r="DO39" t="s">
+        <v>266</v>
+      </c>
+      <c r="DP39" t="s">
+        <v>283</v>
+      </c>
+      <c r="DQ39" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT39">
+        <v>9.35</v>
+      </c>
+      <c r="DV39">
+        <v>4.3</v>
+      </c>
+      <c r="DW39">
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="40" spans="1:127" x14ac:dyDescent="0.25">
@@ -10962,16 +12234,247 @@
       <c r="K40">
         <v>200</v>
       </c>
+      <c r="L40" t="s">
+        <v>88</v>
+      </c>
+      <c r="M40" t="s">
+        <v>88</v>
+      </c>
+      <c r="N40" t="s">
+        <v>89</v>
+      </c>
+      <c r="O40" t="s">
+        <v>88</v>
+      </c>
+      <c r="P40" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>88</v>
+      </c>
+      <c r="R40" t="s">
+        <v>88</v>
+      </c>
+      <c r="S40" t="s">
+        <v>88</v>
+      </c>
+      <c r="T40" t="s">
+        <v>88</v>
+      </c>
+      <c r="U40" t="s">
+        <v>88</v>
+      </c>
+      <c r="V40" t="s">
+        <v>88</v>
+      </c>
+      <c r="W40" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>278</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV40">
+        <v>0</v>
+      </c>
+      <c r="AW40">
+        <v>0</v>
+      </c>
+      <c r="AX40">
+        <v>0</v>
+      </c>
+      <c r="AY40">
+        <v>1</v>
+      </c>
+      <c r="AZ40">
+        <v>0</v>
+      </c>
+      <c r="BA40">
+        <v>0</v>
+      </c>
+      <c r="BB40">
+        <v>0</v>
+      </c>
+      <c r="BC40">
+        <v>0</v>
+      </c>
+      <c r="BD40">
+        <v>3</v>
+      </c>
+      <c r="BE40">
+        <v>0</v>
+      </c>
+      <c r="BF40">
+        <v>0</v>
+      </c>
+      <c r="BG40">
+        <v>0</v>
+      </c>
+      <c r="BH40">
+        <v>0</v>
+      </c>
+      <c r="BI40">
+        <v>0</v>
+      </c>
+      <c r="BJ40">
+        <v>0</v>
+      </c>
+      <c r="BK40">
+        <v>0</v>
+      </c>
+      <c r="BL40">
+        <v>1</v>
+      </c>
+      <c r="BM40">
+        <v>0</v>
+      </c>
+      <c r="BN40">
+        <v>0</v>
+      </c>
+      <c r="BO40">
+        <v>0</v>
+      </c>
+      <c r="BP40">
+        <v>0</v>
+      </c>
+      <c r="BQ40">
+        <v>0</v>
+      </c>
+      <c r="BR40">
+        <v>0</v>
+      </c>
+      <c r="BS40">
+        <v>1</v>
+      </c>
+      <c r="BT40">
+        <v>0</v>
+      </c>
+      <c r="BU40">
+        <v>0</v>
+      </c>
+      <c r="BV40">
+        <v>0</v>
+      </c>
+      <c r="BW40">
+        <v>0</v>
+      </c>
+      <c r="BX40">
+        <v>0</v>
+      </c>
+      <c r="BY40">
+        <v>0</v>
+      </c>
+      <c r="BZ40">
+        <v>0</v>
+      </c>
+      <c r="CA40">
+        <v>1</v>
+      </c>
+      <c r="CB40">
+        <v>0</v>
+      </c>
+      <c r="CC40">
+        <v>0</v>
+      </c>
+      <c r="CD40">
+        <v>0</v>
+      </c>
       <c r="CE40">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CF40">
+        <v>0</v>
+      </c>
+      <c r="CQ40">
+        <v>0</v>
+      </c>
+      <c r="CR40">
+        <v>0</v>
+      </c>
+      <c r="CS40">
+        <v>0</v>
+      </c>
+      <c r="CT40">
+        <v>0</v>
+      </c>
+      <c r="CU40">
+        <v>0</v>
+      </c>
+      <c r="CV40">
+        <v>0</v>
+      </c>
+      <c r="CW40">
+        <v>0</v>
+      </c>
+      <c r="CX40">
+        <v>0</v>
+      </c>
+      <c r="CY40">
+        <v>0</v>
+      </c>
+      <c r="CZ40">
+        <v>0</v>
+      </c>
+      <c r="DA40">
+        <v>0</v>
+      </c>
+      <c r="DB40">
+        <v>0</v>
+      </c>
+      <c r="DC40">
+        <v>0</v>
+      </c>
+      <c r="DD40">
+        <v>0</v>
+      </c>
+      <c r="DE40">
+        <v>0</v>
+      </c>
+      <c r="DF40">
+        <v>0</v>
+      </c>
+      <c r="DG40">
+        <v>0</v>
+      </c>
+      <c r="DH40">
+        <v>0</v>
+      </c>
+      <c r="DI40">
+        <v>0</v>
+      </c>
+      <c r="DJ40">
+        <v>0</v>
+      </c>
+      <c r="DK40">
         <v>0</v>
       </c>
       <c r="DL40">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="DN40" t="s">
+        <v>277</v>
+      </c>
+      <c r="DO40" t="s">
+        <v>266</v>
+      </c>
+      <c r="DP40" t="s">
+        <v>276</v>
+      </c>
+      <c r="DQ40" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT40">
+        <v>7.55</v>
+      </c>
+      <c r="DV40">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DW40">
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="41" spans="1:127" x14ac:dyDescent="0.25">
@@ -11008,16 +12511,241 @@
       <c r="K41">
         <v>200</v>
       </c>
+      <c r="L41" t="s">
+        <v>88</v>
+      </c>
+      <c r="M41" t="s">
+        <v>88</v>
+      </c>
+      <c r="N41" t="s">
+        <v>88</v>
+      </c>
+      <c r="O41" t="s">
+        <v>88</v>
+      </c>
+      <c r="P41" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>88</v>
+      </c>
+      <c r="R41" t="s">
+        <v>88</v>
+      </c>
+      <c r="S41" t="s">
+        <v>88</v>
+      </c>
+      <c r="T41" t="s">
+        <v>88</v>
+      </c>
+      <c r="U41" t="s">
+        <v>88</v>
+      </c>
+      <c r="V41" t="s">
+        <v>88</v>
+      </c>
+      <c r="W41" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV41">
+        <v>0</v>
+      </c>
+      <c r="AW41">
+        <v>0</v>
+      </c>
+      <c r="AX41">
+        <v>1</v>
+      </c>
+      <c r="AY41">
+        <v>0</v>
+      </c>
+      <c r="AZ41">
+        <v>0</v>
+      </c>
+      <c r="BA41">
+        <v>0</v>
+      </c>
+      <c r="BB41">
+        <v>0</v>
+      </c>
+      <c r="BC41">
+        <v>0</v>
+      </c>
+      <c r="BD41">
+        <v>3</v>
+      </c>
+      <c r="BE41">
+        <v>0</v>
+      </c>
+      <c r="BF41">
+        <v>0</v>
+      </c>
+      <c r="BG41">
+        <v>0</v>
+      </c>
+      <c r="BH41">
+        <v>0</v>
+      </c>
+      <c r="BI41">
+        <v>0</v>
+      </c>
+      <c r="BJ41">
+        <v>0</v>
+      </c>
+      <c r="BK41">
+        <v>0</v>
+      </c>
+      <c r="BL41">
+        <v>1</v>
+      </c>
+      <c r="BM41">
+        <v>0</v>
+      </c>
+      <c r="BN41">
+        <v>0</v>
+      </c>
+      <c r="BO41">
+        <v>0</v>
+      </c>
+      <c r="BP41">
+        <v>0</v>
+      </c>
+      <c r="BQ41">
+        <v>0</v>
+      </c>
+      <c r="BR41">
+        <v>0</v>
+      </c>
+      <c r="BS41">
+        <v>1</v>
+      </c>
+      <c r="BT41">
+        <v>0</v>
+      </c>
+      <c r="BU41">
+        <v>0</v>
+      </c>
+      <c r="BV41">
+        <v>0</v>
+      </c>
+      <c r="BW41">
+        <v>0</v>
+      </c>
+      <c r="BX41">
+        <v>0</v>
+      </c>
+      <c r="BY41">
+        <v>0</v>
+      </c>
+      <c r="BZ41">
+        <v>0</v>
+      </c>
+      <c r="CA41">
+        <v>1</v>
+      </c>
+      <c r="CB41">
+        <v>0</v>
+      </c>
+      <c r="CC41">
+        <v>0</v>
+      </c>
+      <c r="CD41">
+        <v>0</v>
+      </c>
       <c r="CE41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CF41">
+        <v>0</v>
+      </c>
+      <c r="CQ41">
+        <v>0</v>
+      </c>
+      <c r="CR41">
+        <v>0</v>
+      </c>
+      <c r="CS41">
+        <v>0</v>
+      </c>
+      <c r="CT41">
+        <v>0</v>
+      </c>
+      <c r="CU41">
+        <v>0</v>
+      </c>
+      <c r="CV41">
+        <v>0</v>
+      </c>
+      <c r="CW41">
+        <v>0</v>
+      </c>
+      <c r="CX41">
+        <v>0</v>
+      </c>
+      <c r="CY41">
+        <v>0</v>
+      </c>
+      <c r="CZ41">
+        <v>0</v>
+      </c>
+      <c r="DA41">
+        <v>0</v>
+      </c>
+      <c r="DB41">
+        <v>0</v>
+      </c>
+      <c r="DC41">
+        <v>0</v>
+      </c>
+      <c r="DD41">
+        <v>0</v>
+      </c>
+      <c r="DE41">
+        <v>0</v>
+      </c>
+      <c r="DF41">
+        <v>0</v>
+      </c>
+      <c r="DG41">
+        <v>0</v>
+      </c>
+      <c r="DH41">
+        <v>0</v>
+      </c>
+      <c r="DI41">
+        <v>0</v>
+      </c>
+      <c r="DJ41">
+        <v>0</v>
+      </c>
+      <c r="DK41">
         <v>0</v>
       </c>
       <c r="DL41">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="DN41" t="s">
+        <v>277</v>
+      </c>
+      <c r="DO41" t="s">
+        <v>266</v>
+      </c>
+      <c r="DP41" t="s">
+        <v>276</v>
+      </c>
+      <c r="DQ41" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT41">
+        <v>7.55</v>
+      </c>
+      <c r="DV41">
+        <v>4.55</v>
+      </c>
+      <c r="DW41">
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:127" x14ac:dyDescent="0.25">
@@ -11054,16 +12782,240 @@
       <c r="K42">
         <v>150</v>
       </c>
+      <c r="L42" t="s">
+        <v>88</v>
+      </c>
+      <c r="M42" t="s">
+        <v>88</v>
+      </c>
+      <c r="N42" t="s">
+        <v>89</v>
+      </c>
+      <c r="O42" t="s">
+        <v>88</v>
+      </c>
+      <c r="P42" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>88</v>
+      </c>
+      <c r="R42" t="s">
+        <v>88</v>
+      </c>
+      <c r="S42" t="s">
+        <v>88</v>
+      </c>
+      <c r="T42" t="s">
+        <v>88</v>
+      </c>
+      <c r="U42" t="s">
+        <v>88</v>
+      </c>
+      <c r="V42" t="s">
+        <v>88</v>
+      </c>
+      <c r="W42" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>278</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV42">
+        <v>0</v>
+      </c>
+      <c r="AW42">
+        <v>1</v>
+      </c>
+      <c r="AX42">
+        <v>0</v>
+      </c>
+      <c r="AY42">
+        <v>0</v>
+      </c>
+      <c r="AZ42">
+        <v>0</v>
+      </c>
+      <c r="BA42">
+        <v>0</v>
+      </c>
+      <c r="BB42">
+        <v>0</v>
+      </c>
+      <c r="BC42">
+        <v>0</v>
+      </c>
+      <c r="BD42">
+        <v>0</v>
+      </c>
+      <c r="BE42">
+        <v>0</v>
+      </c>
+      <c r="BF42">
+        <v>0</v>
+      </c>
+      <c r="BG42">
+        <v>0</v>
+      </c>
+      <c r="BH42">
+        <v>0</v>
+      </c>
+      <c r="BI42">
+        <v>0</v>
+      </c>
+      <c r="BJ42">
+        <v>0</v>
+      </c>
+      <c r="BK42">
+        <v>0</v>
+      </c>
+      <c r="BL42">
+        <v>1</v>
+      </c>
+      <c r="BM42">
+        <v>0</v>
+      </c>
+      <c r="BN42">
+        <v>0</v>
+      </c>
+      <c r="BO42">
+        <v>0</v>
+      </c>
+      <c r="BP42">
+        <v>0</v>
+      </c>
+      <c r="BQ42">
+        <v>0</v>
+      </c>
+      <c r="BR42">
+        <v>1</v>
+      </c>
+      <c r="BS42">
+        <v>0</v>
+      </c>
+      <c r="BT42">
+        <v>0</v>
+      </c>
+      <c r="BU42">
+        <v>0</v>
+      </c>
+      <c r="BV42">
+        <v>0</v>
+      </c>
+      <c r="BW42">
+        <v>0</v>
+      </c>
+      <c r="BX42">
+        <v>0</v>
+      </c>
+      <c r="BY42">
+        <v>0</v>
+      </c>
+      <c r="BZ42">
+        <v>0</v>
+      </c>
+      <c r="CA42">
+        <v>1</v>
+      </c>
+      <c r="CB42">
+        <v>0</v>
+      </c>
+      <c r="CC42">
+        <v>0</v>
+      </c>
+      <c r="CD42">
+        <v>0</v>
+      </c>
       <c r="CE42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CF42">
         <v>0</v>
       </c>
+      <c r="CQ42">
+        <v>0</v>
+      </c>
+      <c r="CR42">
+        <v>0</v>
+      </c>
+      <c r="CS42">
+        <v>0</v>
+      </c>
+      <c r="CT42">
+        <v>0</v>
+      </c>
+      <c r="CU42">
+        <v>0</v>
+      </c>
+      <c r="CV42">
+        <v>0</v>
+      </c>
+      <c r="CW42">
+        <v>0</v>
+      </c>
+      <c r="CX42">
+        <v>0</v>
+      </c>
+      <c r="CY42">
+        <v>0</v>
+      </c>
+      <c r="CZ42">
+        <v>0</v>
+      </c>
+      <c r="DA42">
+        <v>0</v>
+      </c>
+      <c r="DB42">
+        <v>0</v>
+      </c>
+      <c r="DC42">
+        <v>0</v>
+      </c>
+      <c r="DD42">
+        <v>0</v>
+      </c>
+      <c r="DE42">
+        <v>0</v>
+      </c>
+      <c r="DF42">
+        <v>0</v>
+      </c>
+      <c r="DG42">
+        <v>0</v>
+      </c>
+      <c r="DH42">
+        <v>0</v>
+      </c>
+      <c r="DI42">
+        <v>0</v>
+      </c>
+      <c r="DJ42">
+        <v>0</v>
+      </c>
+      <c r="DK42">
+        <v>0</v>
+      </c>
       <c r="DL42">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="DN42" t="s">
+        <v>277</v>
+      </c>
+      <c r="DO42" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT42">
+        <v>7</v>
+      </c>
+      <c r="DV42">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DW42">
+        <v>4.5</v>
       </c>
     </row>
     <row r="43" spans="1:127" x14ac:dyDescent="0.25">
@@ -11100,16 +13052,241 @@
       <c r="K43">
         <v>100</v>
       </c>
+      <c r="L43" t="s">
+        <v>88</v>
+      </c>
+      <c r="M43" t="s">
+        <v>88</v>
+      </c>
+      <c r="N43" t="s">
+        <v>89</v>
+      </c>
+      <c r="O43" t="s">
+        <v>88</v>
+      </c>
+      <c r="P43" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>88</v>
+      </c>
+      <c r="R43" t="s">
+        <v>88</v>
+      </c>
+      <c r="S43" t="s">
+        <v>88</v>
+      </c>
+      <c r="T43" t="s">
+        <v>88</v>
+      </c>
+      <c r="U43" t="s">
+        <v>88</v>
+      </c>
+      <c r="V43" t="s">
+        <v>88</v>
+      </c>
+      <c r="W43" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>278</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV43">
+        <v>1</v>
+      </c>
+      <c r="AW43">
+        <v>0</v>
+      </c>
+      <c r="AX43">
+        <v>0</v>
+      </c>
+      <c r="AY43">
+        <v>0</v>
+      </c>
+      <c r="AZ43">
+        <v>0</v>
+      </c>
+      <c r="BA43">
+        <v>0</v>
+      </c>
+      <c r="BB43">
+        <v>0</v>
+      </c>
+      <c r="BC43">
+        <v>0</v>
+      </c>
+      <c r="BD43">
+        <v>0</v>
+      </c>
+      <c r="BE43">
+        <v>0</v>
+      </c>
+      <c r="BF43">
+        <v>0</v>
+      </c>
+      <c r="BG43">
+        <v>0</v>
+      </c>
+      <c r="BH43">
+        <v>0</v>
+      </c>
+      <c r="BI43">
+        <v>0</v>
+      </c>
+      <c r="BJ43">
+        <v>0</v>
+      </c>
+      <c r="BK43">
+        <v>0</v>
+      </c>
+      <c r="BL43">
+        <v>1</v>
+      </c>
+      <c r="BM43">
+        <v>0</v>
+      </c>
+      <c r="BN43">
+        <v>0</v>
+      </c>
+      <c r="BO43">
+        <v>0</v>
+      </c>
+      <c r="BP43">
+        <v>0</v>
+      </c>
+      <c r="BQ43">
+        <v>1</v>
+      </c>
+      <c r="BR43">
+        <v>0</v>
+      </c>
+      <c r="BS43">
+        <v>0</v>
+      </c>
+      <c r="BT43">
+        <v>0</v>
+      </c>
+      <c r="BU43">
+        <v>0</v>
+      </c>
+      <c r="BV43">
+        <v>0</v>
+      </c>
+      <c r="BW43">
+        <v>0</v>
+      </c>
+      <c r="BX43">
+        <v>0</v>
+      </c>
+      <c r="BY43">
+        <v>0</v>
+      </c>
+      <c r="BZ43">
+        <v>0</v>
+      </c>
+      <c r="CA43">
+        <v>1</v>
+      </c>
+      <c r="CB43">
+        <v>0</v>
+      </c>
+      <c r="CC43">
+        <v>0</v>
+      </c>
+      <c r="CD43">
+        <v>0</v>
+      </c>
       <c r="CE43">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CF43">
+        <v>0</v>
+      </c>
+      <c r="CQ43">
+        <v>0</v>
+      </c>
+      <c r="CR43">
+        <v>0</v>
+      </c>
+      <c r="CS43">
+        <v>0</v>
+      </c>
+      <c r="CT43">
+        <v>0</v>
+      </c>
+      <c r="CU43">
+        <v>0</v>
+      </c>
+      <c r="CV43">
+        <v>0</v>
+      </c>
+      <c r="CW43">
+        <v>0</v>
+      </c>
+      <c r="CX43">
+        <v>0</v>
+      </c>
+      <c r="CY43">
+        <v>0</v>
+      </c>
+      <c r="CZ43">
+        <v>0</v>
+      </c>
+      <c r="DA43">
+        <v>0</v>
+      </c>
+      <c r="DB43">
+        <v>0</v>
+      </c>
+      <c r="DC43">
+        <v>0</v>
+      </c>
+      <c r="DD43">
+        <v>0</v>
+      </c>
+      <c r="DE43">
+        <v>0</v>
+      </c>
+      <c r="DF43">
+        <v>0</v>
+      </c>
+      <c r="DG43">
+        <v>0</v>
+      </c>
+      <c r="DH43">
+        <v>0</v>
+      </c>
+      <c r="DI43">
+        <v>0</v>
+      </c>
+      <c r="DJ43">
+        <v>0</v>
+      </c>
+      <c r="DK43">
         <v>0</v>
       </c>
       <c r="DL43">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="DN43" t="s">
+        <v>277</v>
+      </c>
+      <c r="DO43" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT43">
+        <v>5.8</v>
+      </c>
+      <c r="DV43">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DW43">
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:127" x14ac:dyDescent="0.25">
@@ -11146,16 +13323,238 @@
       <c r="K44">
         <v>150</v>
       </c>
+      <c r="L44" t="s">
+        <v>88</v>
+      </c>
+      <c r="M44" t="s">
+        <v>88</v>
+      </c>
+      <c r="O44" t="s">
+        <v>88</v>
+      </c>
+      <c r="P44" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>88</v>
+      </c>
+      <c r="R44" t="s">
+        <v>88</v>
+      </c>
+      <c r="S44" t="s">
+        <v>88</v>
+      </c>
+      <c r="T44" t="s">
+        <v>88</v>
+      </c>
+      <c r="U44" t="s">
+        <v>89</v>
+      </c>
+      <c r="V44" t="s">
+        <v>88</v>
+      </c>
+      <c r="W44" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>266</v>
+      </c>
+      <c r="AP44" t="s">
+        <v>290</v>
+      </c>
+      <c r="AQ44" t="s">
+        <v>279</v>
+      </c>
+      <c r="AV44">
+        <v>0</v>
+      </c>
+      <c r="AW44">
+        <v>0</v>
+      </c>
+      <c r="AX44">
+        <v>0</v>
+      </c>
+      <c r="AY44">
+        <v>0</v>
+      </c>
+      <c r="AZ44">
+        <v>1</v>
+      </c>
+      <c r="BA44">
+        <v>0</v>
+      </c>
+      <c r="BB44">
+        <v>0</v>
+      </c>
+      <c r="BC44">
+        <v>0</v>
+      </c>
+      <c r="BD44">
+        <v>0</v>
+      </c>
+      <c r="BE44">
+        <v>2</v>
+      </c>
+      <c r="BF44">
+        <v>0</v>
+      </c>
+      <c r="BG44">
+        <v>0</v>
+      </c>
+      <c r="BH44">
+        <v>0</v>
+      </c>
+      <c r="BI44">
+        <v>0</v>
+      </c>
+      <c r="BJ44">
+        <v>0</v>
+      </c>
+      <c r="BK44">
+        <v>0</v>
+      </c>
+      <c r="BL44">
+        <v>1</v>
+      </c>
+      <c r="BM44">
+        <v>0</v>
+      </c>
+      <c r="BN44">
+        <v>0</v>
+      </c>
+      <c r="BO44">
+        <v>0</v>
+      </c>
+      <c r="BP44">
+        <v>0</v>
+      </c>
+      <c r="BQ44">
+        <v>0</v>
+      </c>
+      <c r="BR44">
+        <v>0</v>
+      </c>
+      <c r="BS44">
+        <v>1</v>
+      </c>
+      <c r="BT44">
+        <v>0</v>
+      </c>
+      <c r="BU44">
+        <v>0</v>
+      </c>
+      <c r="BV44">
+        <v>0</v>
+      </c>
+      <c r="BW44">
+        <v>0</v>
+      </c>
+      <c r="BX44">
+        <v>0</v>
+      </c>
+      <c r="BY44">
+        <v>0</v>
+      </c>
+      <c r="BZ44">
+        <v>0</v>
+      </c>
+      <c r="CA44">
+        <v>0</v>
+      </c>
+      <c r="CB44">
+        <v>1</v>
+      </c>
+      <c r="CC44">
+        <v>0</v>
+      </c>
+      <c r="CD44">
+        <v>0</v>
+      </c>
       <c r="CE44">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF44">
+        <v>0</v>
+      </c>
+      <c r="CQ44">
+        <v>0</v>
+      </c>
+      <c r="CR44">
+        <v>0</v>
+      </c>
+      <c r="CS44">
+        <v>0</v>
+      </c>
+      <c r="CT44">
+        <v>1</v>
+      </c>
+      <c r="CU44">
+        <v>0</v>
+      </c>
+      <c r="CV44">
+        <v>0</v>
+      </c>
+      <c r="CW44">
+        <v>0</v>
+      </c>
+      <c r="CX44">
+        <v>0</v>
+      </c>
+      <c r="CY44">
+        <v>0</v>
+      </c>
+      <c r="CZ44">
+        <v>0</v>
+      </c>
+      <c r="DA44">
+        <v>1</v>
+      </c>
+      <c r="DB44">
+        <v>0</v>
+      </c>
+      <c r="DC44">
+        <v>0</v>
+      </c>
+      <c r="DD44">
+        <v>0</v>
+      </c>
+      <c r="DE44">
+        <v>0</v>
+      </c>
+      <c r="DF44">
+        <v>0</v>
+      </c>
+      <c r="DG44">
+        <v>0</v>
+      </c>
+      <c r="DH44">
+        <v>0</v>
+      </c>
+      <c r="DI44">
+        <v>0</v>
+      </c>
+      <c r="DJ44">
+        <v>0</v>
+      </c>
+      <c r="DK44">
         <v>0</v>
       </c>
       <c r="DL44">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="DT44">
+        <v>5.5</v>
+      </c>
+      <c r="DV44">
+        <v>2.4</v>
+      </c>
+      <c r="DW44">
+        <v>2.9</v>
       </c>
     </row>
     <row r="45" spans="1:127" x14ac:dyDescent="0.25">
@@ -11192,16 +13591,229 @@
       <c r="K45">
         <v>1100</v>
       </c>
+      <c r="L45" t="s">
+        <v>88</v>
+      </c>
+      <c r="M45" t="s">
+        <v>88</v>
+      </c>
+      <c r="N45" t="s">
+        <v>88</v>
+      </c>
+      <c r="O45" t="s">
+        <v>88</v>
+      </c>
+      <c r="P45" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>88</v>
+      </c>
+      <c r="R45" t="s">
+        <v>88</v>
+      </c>
+      <c r="S45" t="s">
+        <v>88</v>
+      </c>
+      <c r="T45" t="s">
+        <v>88</v>
+      </c>
+      <c r="U45" t="s">
+        <v>88</v>
+      </c>
+      <c r="V45" t="s">
+        <v>88</v>
+      </c>
+      <c r="W45" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV45">
+        <v>0</v>
+      </c>
+      <c r="AW45">
+        <v>0</v>
+      </c>
+      <c r="AX45">
+        <v>0</v>
+      </c>
+      <c r="AY45">
+        <v>0</v>
+      </c>
+      <c r="AZ45">
+        <v>0</v>
+      </c>
+      <c r="BA45">
+        <v>1</v>
+      </c>
+      <c r="BB45">
+        <v>0</v>
+      </c>
+      <c r="BC45">
+        <v>0</v>
+      </c>
+      <c r="BD45">
+        <v>0</v>
+      </c>
+      <c r="BE45">
+        <v>0</v>
+      </c>
+      <c r="BF45">
+        <v>0</v>
+      </c>
+      <c r="BG45">
+        <v>0</v>
+      </c>
+      <c r="BH45">
+        <v>0</v>
+      </c>
+      <c r="BI45">
+        <v>0</v>
+      </c>
+      <c r="BJ45">
+        <v>0</v>
+      </c>
+      <c r="BK45">
+        <v>0</v>
+      </c>
+      <c r="BL45">
+        <v>0</v>
+      </c>
+      <c r="BM45">
+        <v>0</v>
+      </c>
+      <c r="BN45">
+        <v>1</v>
+      </c>
+      <c r="BO45">
+        <v>0</v>
+      </c>
+      <c r="BP45">
+        <v>0</v>
+      </c>
+      <c r="BQ45">
+        <v>0</v>
+      </c>
+      <c r="BR45">
+        <v>0</v>
+      </c>
+      <c r="BS45">
+        <v>0</v>
+      </c>
+      <c r="BT45">
+        <v>0</v>
+      </c>
+      <c r="BU45">
+        <v>1</v>
+      </c>
+      <c r="BV45">
+        <v>0</v>
+      </c>
+      <c r="BW45">
+        <v>0</v>
+      </c>
+      <c r="BX45">
+        <v>0</v>
+      </c>
+      <c r="BY45">
+        <v>0</v>
+      </c>
+      <c r="BZ45">
+        <v>0</v>
+      </c>
+      <c r="CA45">
+        <v>0</v>
+      </c>
+      <c r="CB45">
+        <v>0</v>
+      </c>
+      <c r="CC45">
+        <v>1</v>
+      </c>
+      <c r="CD45">
+        <v>0</v>
+      </c>
       <c r="CE45">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CF45">
+        <v>0</v>
+      </c>
+      <c r="CQ45">
+        <v>0</v>
+      </c>
+      <c r="CR45">
+        <v>0</v>
+      </c>
+      <c r="CS45">
+        <v>0</v>
+      </c>
+      <c r="CT45">
+        <v>0</v>
+      </c>
+      <c r="CU45">
+        <v>1</v>
+      </c>
+      <c r="CV45">
+        <v>0</v>
+      </c>
+      <c r="CW45">
+        <v>0</v>
+      </c>
+      <c r="CX45">
+        <v>0</v>
+      </c>
+      <c r="CY45">
+        <v>0</v>
+      </c>
+      <c r="CZ45">
+        <v>0</v>
+      </c>
+      <c r="DA45">
+        <v>0</v>
+      </c>
+      <c r="DB45">
+        <v>0</v>
+      </c>
+      <c r="DC45">
+        <v>0</v>
+      </c>
+      <c r="DD45">
+        <v>0</v>
+      </c>
+      <c r="DE45">
+        <v>0</v>
+      </c>
+      <c r="DF45">
+        <v>0</v>
+      </c>
+      <c r="DG45">
+        <v>0</v>
+      </c>
+      <c r="DH45">
+        <v>0</v>
+      </c>
+      <c r="DI45">
+        <v>0</v>
+      </c>
+      <c r="DJ45">
+        <v>0</v>
+      </c>
+      <c r="DK45">
         <v>0</v>
       </c>
       <c r="DL45">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DT45">
+        <v>15.5</v>
+      </c>
+      <c r="DV45">
+        <v>5.65</v>
+      </c>
+      <c r="DW45">
+        <v>6.3</v>
       </c>
     </row>
     <row r="46" spans="1:127" x14ac:dyDescent="0.25">
@@ -11238,16 +13850,229 @@
       <c r="K46">
         <v>400</v>
       </c>
+      <c r="L46" t="s">
+        <v>88</v>
+      </c>
+      <c r="M46" t="s">
+        <v>88</v>
+      </c>
+      <c r="N46" t="s">
+        <v>88</v>
+      </c>
+      <c r="O46" t="s">
+        <v>88</v>
+      </c>
+      <c r="P46" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>88</v>
+      </c>
+      <c r="R46" t="s">
+        <v>88</v>
+      </c>
+      <c r="S46" t="s">
+        <v>88</v>
+      </c>
+      <c r="T46" t="s">
+        <v>88</v>
+      </c>
+      <c r="U46" t="s">
+        <v>88</v>
+      </c>
+      <c r="V46" t="s">
+        <v>88</v>
+      </c>
+      <c r="W46" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV46">
+        <v>0</v>
+      </c>
+      <c r="AW46">
+        <v>0</v>
+      </c>
+      <c r="AX46">
+        <v>0</v>
+      </c>
+      <c r="AY46">
+        <v>1</v>
+      </c>
+      <c r="AZ46">
+        <v>0</v>
+      </c>
+      <c r="BA46">
+        <v>0</v>
+      </c>
+      <c r="BB46">
+        <v>0</v>
+      </c>
+      <c r="BC46">
+        <v>0</v>
+      </c>
+      <c r="BD46">
+        <v>0</v>
+      </c>
+      <c r="BE46">
+        <v>0</v>
+      </c>
+      <c r="BF46">
+        <v>0</v>
+      </c>
+      <c r="BG46">
+        <v>0</v>
+      </c>
+      <c r="BH46">
+        <v>0</v>
+      </c>
+      <c r="BI46">
+        <v>0</v>
+      </c>
+      <c r="BJ46">
+        <v>0</v>
+      </c>
+      <c r="BK46">
+        <v>0</v>
+      </c>
+      <c r="BL46">
+        <v>0</v>
+      </c>
+      <c r="BM46">
+        <v>1</v>
+      </c>
+      <c r="BN46">
+        <v>0</v>
+      </c>
+      <c r="BO46">
+        <v>0</v>
+      </c>
+      <c r="BP46">
+        <v>0</v>
+      </c>
+      <c r="BQ46">
+        <v>0</v>
+      </c>
+      <c r="BR46">
+        <v>0</v>
+      </c>
+      <c r="BS46">
+        <v>0</v>
+      </c>
+      <c r="BT46">
+        <v>1</v>
+      </c>
+      <c r="BU46">
+        <v>0</v>
+      </c>
+      <c r="BV46">
+        <v>0</v>
+      </c>
+      <c r="BW46">
+        <v>0</v>
+      </c>
+      <c r="BX46">
+        <v>0</v>
+      </c>
+      <c r="BY46">
+        <v>0</v>
+      </c>
+      <c r="BZ46">
+        <v>0</v>
+      </c>
+      <c r="CA46">
+        <v>0</v>
+      </c>
+      <c r="CB46">
+        <v>1</v>
+      </c>
+      <c r="CC46">
+        <v>0</v>
+      </c>
+      <c r="CD46">
+        <v>0</v>
+      </c>
       <c r="CE46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CF46">
+        <v>0</v>
+      </c>
+      <c r="CQ46">
+        <v>0</v>
+      </c>
+      <c r="CR46">
+        <v>0</v>
+      </c>
+      <c r="CS46">
+        <v>0</v>
+      </c>
+      <c r="CT46">
+        <v>1</v>
+      </c>
+      <c r="CU46">
+        <v>0</v>
+      </c>
+      <c r="CV46">
+        <v>0</v>
+      </c>
+      <c r="CW46">
+        <v>0</v>
+      </c>
+      <c r="CX46">
+        <v>0</v>
+      </c>
+      <c r="CY46">
+        <v>0</v>
+      </c>
+      <c r="CZ46">
+        <v>0</v>
+      </c>
+      <c r="DA46">
+        <v>0</v>
+      </c>
+      <c r="DB46">
+        <v>0</v>
+      </c>
+      <c r="DC46">
+        <v>0</v>
+      </c>
+      <c r="DD46">
+        <v>0</v>
+      </c>
+      <c r="DE46">
+        <v>0</v>
+      </c>
+      <c r="DF46">
+        <v>0</v>
+      </c>
+      <c r="DG46">
+        <v>0</v>
+      </c>
+      <c r="DH46">
+        <v>0</v>
+      </c>
+      <c r="DI46">
+        <v>0</v>
+      </c>
+      <c r="DJ46">
+        <v>0</v>
+      </c>
+      <c r="DK46">
         <v>0</v>
       </c>
       <c r="DL46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DT46">
+        <v>11.98</v>
+      </c>
+      <c r="DV46">
+        <v>3.6</v>
+      </c>
+      <c r="DW46">
+        <v>4.3</v>
       </c>
     </row>
     <row r="47" spans="1:127" x14ac:dyDescent="0.25">
@@ -11284,16 +14109,229 @@
       <c r="K47">
         <v>900</v>
       </c>
+      <c r="L47" t="s">
+        <v>88</v>
+      </c>
+      <c r="M47" t="s">
+        <v>88</v>
+      </c>
+      <c r="N47" t="s">
+        <v>88</v>
+      </c>
+      <c r="O47" t="s">
+        <v>88</v>
+      </c>
+      <c r="P47" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>88</v>
+      </c>
+      <c r="R47" t="s">
+        <v>88</v>
+      </c>
+      <c r="S47" t="s">
+        <v>88</v>
+      </c>
+      <c r="T47" t="s">
+        <v>88</v>
+      </c>
+      <c r="U47" t="s">
+        <v>88</v>
+      </c>
+      <c r="V47" t="s">
+        <v>88</v>
+      </c>
+      <c r="W47" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV47">
+        <v>0</v>
+      </c>
+      <c r="AW47">
+        <v>0</v>
+      </c>
+      <c r="AX47">
+        <v>0</v>
+      </c>
+      <c r="AY47">
+        <v>0</v>
+      </c>
+      <c r="AZ47">
+        <v>0</v>
+      </c>
+      <c r="BA47">
+        <v>1</v>
+      </c>
+      <c r="BB47">
+        <v>0</v>
+      </c>
+      <c r="BC47">
+        <v>0</v>
+      </c>
+      <c r="BD47">
+        <v>0</v>
+      </c>
+      <c r="BE47">
+        <v>0</v>
+      </c>
+      <c r="BF47">
+        <v>0</v>
+      </c>
+      <c r="BG47">
+        <v>0</v>
+      </c>
+      <c r="BH47">
+        <v>0</v>
+      </c>
+      <c r="BI47">
+        <v>0</v>
+      </c>
+      <c r="BJ47">
+        <v>0</v>
+      </c>
+      <c r="BK47">
+        <v>0</v>
+      </c>
+      <c r="BL47">
+        <v>0</v>
+      </c>
+      <c r="BM47">
+        <v>0</v>
+      </c>
+      <c r="BN47">
+        <v>1</v>
+      </c>
+      <c r="BO47">
+        <v>0</v>
+      </c>
+      <c r="BP47">
+        <v>0</v>
+      </c>
+      <c r="BQ47">
+        <v>0</v>
+      </c>
+      <c r="BR47">
+        <v>0</v>
+      </c>
+      <c r="BS47">
+        <v>0</v>
+      </c>
+      <c r="BT47">
+        <v>0</v>
+      </c>
+      <c r="BU47">
+        <v>1</v>
+      </c>
+      <c r="BV47">
+        <v>0</v>
+      </c>
+      <c r="BW47">
+        <v>0</v>
+      </c>
+      <c r="BX47">
+        <v>0</v>
+      </c>
+      <c r="BY47">
+        <v>0</v>
+      </c>
+      <c r="BZ47">
+        <v>0</v>
+      </c>
+      <c r="CA47">
+        <v>0</v>
+      </c>
+      <c r="CB47">
+        <v>0</v>
+      </c>
+      <c r="CC47">
+        <v>1</v>
+      </c>
+      <c r="CD47">
+        <v>0</v>
+      </c>
       <c r="CE47">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CF47">
+        <v>0</v>
+      </c>
+      <c r="CQ47">
+        <v>0</v>
+      </c>
+      <c r="CR47">
+        <v>0</v>
+      </c>
+      <c r="CS47">
+        <v>0</v>
+      </c>
+      <c r="CT47">
+        <v>0</v>
+      </c>
+      <c r="CU47">
+        <v>1</v>
+      </c>
+      <c r="CV47">
+        <v>0</v>
+      </c>
+      <c r="CW47">
+        <v>0</v>
+      </c>
+      <c r="CX47">
+        <v>0</v>
+      </c>
+      <c r="CY47">
+        <v>0</v>
+      </c>
+      <c r="CZ47">
+        <v>0</v>
+      </c>
+      <c r="DA47">
+        <v>0</v>
+      </c>
+      <c r="DB47">
+        <v>0</v>
+      </c>
+      <c r="DC47">
+        <v>0</v>
+      </c>
+      <c r="DD47">
+        <v>0</v>
+      </c>
+      <c r="DE47">
+        <v>0</v>
+      </c>
+      <c r="DF47">
+        <v>0</v>
+      </c>
+      <c r="DG47">
+        <v>0</v>
+      </c>
+      <c r="DH47">
+        <v>0</v>
+      </c>
+      <c r="DI47">
+        <v>0</v>
+      </c>
+      <c r="DJ47">
+        <v>0</v>
+      </c>
+      <c r="DK47">
         <v>0</v>
       </c>
       <c r="DL47">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DT47">
+        <v>15.2</v>
+      </c>
+      <c r="DV47">
+        <v>4.8</v>
+      </c>
+      <c r="DW47">
+        <v>5.6</v>
       </c>
     </row>
     <row r="48" spans="1:127" x14ac:dyDescent="0.25">
@@ -11321,7 +14359,7 @@
       <c r="H48" t="s">
         <v>139</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="4">
         <v>7336875</v>
       </c>
       <c r="J48" t="s">
@@ -11342,7 +14380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -11367,7 +14405,7 @@
       <c r="H49" t="s">
         <v>140</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="4">
         <v>7329822</v>
       </c>
       <c r="J49" t="s">
@@ -11388,7 +14426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -11422,19 +14460,232 @@
       <c r="K50">
         <v>450</v>
       </c>
+      <c r="L50" t="s">
+        <v>88</v>
+      </c>
+      <c r="M50" t="s">
+        <v>88</v>
+      </c>
+      <c r="N50" t="s">
+        <v>88</v>
+      </c>
+      <c r="O50" t="s">
+        <v>88</v>
+      </c>
+      <c r="P50" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>88</v>
+      </c>
+      <c r="R50" t="s">
+        <v>88</v>
+      </c>
+      <c r="S50" t="s">
+        <v>88</v>
+      </c>
+      <c r="T50" t="s">
+        <v>88</v>
+      </c>
+      <c r="U50" t="s">
+        <v>88</v>
+      </c>
+      <c r="V50" t="s">
+        <v>88</v>
+      </c>
+      <c r="W50" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV50">
+        <v>0</v>
+      </c>
+      <c r="AW50">
+        <v>0</v>
+      </c>
+      <c r="AX50">
+        <v>0</v>
+      </c>
+      <c r="AY50">
+        <v>0</v>
+      </c>
+      <c r="AZ50">
+        <v>0</v>
+      </c>
+      <c r="BA50">
+        <v>1</v>
+      </c>
+      <c r="BB50">
+        <v>0</v>
+      </c>
+      <c r="BC50">
+        <v>0</v>
+      </c>
+      <c r="BD50">
+        <v>0</v>
+      </c>
+      <c r="BE50">
+        <v>0</v>
+      </c>
+      <c r="BF50">
+        <v>0</v>
+      </c>
+      <c r="BG50">
+        <v>2</v>
+      </c>
+      <c r="BH50">
+        <v>0</v>
+      </c>
+      <c r="BI50">
+        <v>0</v>
+      </c>
+      <c r="BJ50">
+        <v>0</v>
+      </c>
+      <c r="BK50">
+        <v>0</v>
+      </c>
+      <c r="BL50">
+        <v>0</v>
+      </c>
+      <c r="BM50">
+        <v>0</v>
+      </c>
+      <c r="BN50">
+        <v>1</v>
+      </c>
+      <c r="BO50">
+        <v>0</v>
+      </c>
+      <c r="BP50">
+        <v>0</v>
+      </c>
+      <c r="BQ50">
+        <v>0</v>
+      </c>
+      <c r="BR50">
+        <v>0</v>
+      </c>
+      <c r="BS50">
+        <v>0</v>
+      </c>
+      <c r="BT50">
+        <v>0</v>
+      </c>
+      <c r="BU50">
+        <v>1</v>
+      </c>
+      <c r="BV50">
+        <v>0</v>
+      </c>
+      <c r="BW50">
+        <v>0</v>
+      </c>
+      <c r="BX50">
+        <v>0</v>
+      </c>
+      <c r="BY50">
+        <v>0</v>
+      </c>
+      <c r="BZ50">
+        <v>0</v>
+      </c>
+      <c r="CA50">
+        <v>0</v>
+      </c>
+      <c r="CB50">
+        <v>0</v>
+      </c>
+      <c r="CC50">
+        <v>1</v>
+      </c>
+      <c r="CD50">
+        <v>0</v>
+      </c>
       <c r="CE50">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF50">
+        <v>0</v>
+      </c>
+      <c r="CQ50">
+        <v>0</v>
+      </c>
+      <c r="CR50">
+        <v>0</v>
+      </c>
+      <c r="CS50">
+        <v>0</v>
+      </c>
+      <c r="CT50">
+        <v>0</v>
+      </c>
+      <c r="CU50">
+        <v>0</v>
+      </c>
+      <c r="CV50">
+        <v>1</v>
+      </c>
+      <c r="CW50">
+        <v>0</v>
+      </c>
+      <c r="CX50">
+        <v>0</v>
+      </c>
+      <c r="CY50">
+        <v>0</v>
+      </c>
+      <c r="CZ50">
+        <v>0</v>
+      </c>
+      <c r="DA50">
+        <v>0</v>
+      </c>
+      <c r="DB50">
+        <v>0</v>
+      </c>
+      <c r="DC50">
+        <v>1</v>
+      </c>
+      <c r="DD50">
+        <v>0</v>
+      </c>
+      <c r="DE50">
+        <v>0</v>
+      </c>
+      <c r="DF50">
+        <v>0</v>
+      </c>
+      <c r="DG50">
+        <v>0</v>
+      </c>
+      <c r="DH50">
+        <v>0</v>
+      </c>
+      <c r="DI50">
+        <v>0</v>
+      </c>
+      <c r="DJ50">
+        <v>0</v>
+      </c>
+      <c r="DK50">
         <v>0</v>
       </c>
       <c r="DL50">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="DT50">
+        <v>12.4</v>
+      </c>
+      <c r="DV50">
+        <v>3.4</v>
+      </c>
+      <c r="DW50">
+        <v>3.5</v>
       </c>
     </row>
-    <row r="51" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -11468,19 +14719,253 @@
       <c r="K51">
         <v>50</v>
       </c>
+      <c r="L51" t="s">
+        <v>89</v>
+      </c>
+      <c r="M51" t="s">
+        <v>88</v>
+      </c>
+      <c r="O51" t="s">
+        <v>88</v>
+      </c>
+      <c r="P51" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>88</v>
+      </c>
+      <c r="R51" t="s">
+        <v>88</v>
+      </c>
+      <c r="S51" t="s">
+        <v>89</v>
+      </c>
+      <c r="T51" t="s">
+        <v>88</v>
+      </c>
+      <c r="U51" t="s">
+        <v>88</v>
+      </c>
+      <c r="V51" t="s">
+        <v>88</v>
+      </c>
+      <c r="W51" t="s">
+        <v>88</v>
+      </c>
+      <c r="X51" t="s">
+        <v>308</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>266</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>273</v>
+      </c>
+      <c r="AM51" t="s">
+        <v>274</v>
+      </c>
+      <c r="AV51">
+        <v>0</v>
+      </c>
+      <c r="AW51">
+        <v>1</v>
+      </c>
+      <c r="AX51">
+        <v>0</v>
+      </c>
+      <c r="AY51">
+        <v>0</v>
+      </c>
+      <c r="AZ51">
+        <v>0</v>
+      </c>
+      <c r="BA51">
+        <v>0</v>
+      </c>
+      <c r="BB51">
+        <v>0</v>
+      </c>
+      <c r="BC51">
+        <v>0</v>
+      </c>
+      <c r="BD51">
+        <v>0</v>
+      </c>
+      <c r="BE51">
+        <v>0</v>
+      </c>
+      <c r="BF51">
+        <v>0</v>
+      </c>
+      <c r="BG51">
+        <v>0</v>
+      </c>
+      <c r="BH51">
+        <v>0</v>
+      </c>
+      <c r="BI51">
+        <v>0</v>
+      </c>
+      <c r="BJ51">
+        <v>0</v>
+      </c>
+      <c r="BK51">
+        <v>0</v>
+      </c>
+      <c r="BL51">
+        <v>1</v>
+      </c>
+      <c r="BM51">
+        <v>0</v>
+      </c>
+      <c r="BN51">
+        <v>0</v>
+      </c>
+      <c r="BO51">
+        <v>0</v>
+      </c>
+      <c r="BP51">
+        <v>0</v>
+      </c>
+      <c r="BQ51">
+        <v>0</v>
+      </c>
+      <c r="BR51">
+        <v>1</v>
+      </c>
+      <c r="BS51">
+        <v>0</v>
+      </c>
+      <c r="BT51">
+        <v>0</v>
+      </c>
+      <c r="BU51">
+        <v>0</v>
+      </c>
+      <c r="BV51">
+        <v>0</v>
+      </c>
+      <c r="BW51">
+        <v>0</v>
+      </c>
+      <c r="BX51">
+        <v>0</v>
+      </c>
+      <c r="BY51">
+        <v>1</v>
+      </c>
+      <c r="BZ51">
+        <v>0</v>
+      </c>
+      <c r="CA51">
+        <v>0</v>
+      </c>
+      <c r="CB51">
+        <v>0</v>
+      </c>
+      <c r="CC51">
+        <v>0</v>
+      </c>
+      <c r="CD51">
+        <v>0</v>
+      </c>
       <c r="CE51">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CF51">
+        <v>0</v>
+      </c>
+      <c r="CQ51">
+        <v>0</v>
+      </c>
+      <c r="CR51">
+        <v>0</v>
+      </c>
+      <c r="CS51">
+        <v>0</v>
+      </c>
+      <c r="CT51">
+        <v>0</v>
+      </c>
+      <c r="CU51">
+        <v>0</v>
+      </c>
+      <c r="CV51">
+        <v>0</v>
+      </c>
+      <c r="CW51">
+        <v>0</v>
+      </c>
+      <c r="CX51">
+        <v>0</v>
+      </c>
+      <c r="CY51">
+        <v>0</v>
+      </c>
+      <c r="CZ51">
+        <v>0</v>
+      </c>
+      <c r="DA51">
+        <v>1</v>
+      </c>
+      <c r="DB51">
+        <v>0</v>
+      </c>
+      <c r="DC51">
+        <v>0</v>
+      </c>
+      <c r="DD51">
+        <v>0</v>
+      </c>
+      <c r="DE51">
+        <v>0</v>
+      </c>
+      <c r="DF51">
+        <v>0</v>
+      </c>
+      <c r="DG51">
+        <v>0</v>
+      </c>
+      <c r="DH51">
+        <v>0</v>
+      </c>
+      <c r="DI51">
+        <v>0</v>
+      </c>
+      <c r="DJ51">
+        <v>0</v>
+      </c>
+      <c r="DK51">
         <v>0</v>
       </c>
       <c r="DL51">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DN51" t="s">
+        <v>277</v>
+      </c>
+      <c r="DO51" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT51">
+        <v>5.6</v>
+      </c>
+      <c r="DV51">
+        <v>2.4</v>
+      </c>
+      <c r="DW51">
+        <v>2.85</v>
       </c>
     </row>
-    <row r="52" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11514,19 +14999,277 @@
       <c r="K52">
         <v>850</v>
       </c>
+      <c r="L52" t="s">
+        <v>88</v>
+      </c>
+      <c r="M52" t="s">
+        <v>88</v>
+      </c>
+      <c r="N52" t="s">
+        <v>89</v>
+      </c>
+      <c r="O52" t="s">
+        <v>88</v>
+      </c>
+      <c r="P52" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>88</v>
+      </c>
+      <c r="R52" t="s">
+        <v>89</v>
+      </c>
+      <c r="S52" t="s">
+        <v>89</v>
+      </c>
+      <c r="T52" t="s">
+        <v>88</v>
+      </c>
+      <c r="U52" t="s">
+        <v>89</v>
+      </c>
+      <c r="W52" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF52" t="s">
+        <v>273</v>
+      </c>
+      <c r="AG52" t="s">
+        <v>274</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>273</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>274</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>273</v>
+      </c>
+      <c r="AM52" t="s">
+        <v>274</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>275</v>
+      </c>
+      <c r="AQ52" t="s">
+        <v>266</v>
+      </c>
+      <c r="AR52" t="s">
+        <v>226</v>
+      </c>
+      <c r="AS52" t="s">
+        <v>227</v>
+      </c>
+      <c r="AV52">
+        <v>0</v>
+      </c>
+      <c r="AW52">
+        <v>0</v>
+      </c>
+      <c r="AX52">
+        <v>0</v>
+      </c>
+      <c r="AY52">
+        <v>0</v>
+      </c>
+      <c r="AZ52">
+        <v>0</v>
+      </c>
+      <c r="BA52">
+        <v>0</v>
+      </c>
+      <c r="BB52" s="5">
+        <v>1</v>
+      </c>
+      <c r="BC52">
+        <v>0</v>
+      </c>
+      <c r="BD52">
+        <v>0</v>
+      </c>
+      <c r="BE52">
+        <v>0</v>
+      </c>
+      <c r="BF52">
+        <v>0</v>
+      </c>
+      <c r="BG52">
+        <v>0</v>
+      </c>
+      <c r="BH52">
+        <v>2</v>
+      </c>
+      <c r="BI52">
+        <v>0</v>
+      </c>
+      <c r="BJ52">
+        <v>0</v>
+      </c>
+      <c r="BK52">
+        <v>0</v>
+      </c>
+      <c r="BL52">
+        <v>0</v>
+      </c>
+      <c r="BM52">
+        <v>0</v>
+      </c>
+      <c r="BN52">
+        <v>0</v>
+      </c>
+      <c r="BO52">
+        <v>1</v>
+      </c>
+      <c r="BP52">
+        <v>0</v>
+      </c>
+      <c r="BQ52">
+        <v>0</v>
+      </c>
+      <c r="BR52">
+        <v>0</v>
+      </c>
+      <c r="BS52">
+        <v>0</v>
+      </c>
+      <c r="BT52">
+        <v>0</v>
+      </c>
+      <c r="BU52">
+        <v>0</v>
+      </c>
+      <c r="BV52">
+        <v>1</v>
+      </c>
+      <c r="BW52">
+        <v>0</v>
+      </c>
+      <c r="BX52">
+        <v>0</v>
+      </c>
+      <c r="BY52">
+        <v>0</v>
+      </c>
+      <c r="BZ52">
+        <v>0</v>
+      </c>
+      <c r="CA52">
+        <v>0</v>
+      </c>
+      <c r="CB52">
+        <v>0</v>
+      </c>
+      <c r="CC52">
+        <v>1</v>
+      </c>
+      <c r="CD52">
+        <v>0</v>
+      </c>
       <c r="CE52">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF52">
+        <v>0</v>
+      </c>
+      <c r="CQ52">
+        <v>0</v>
+      </c>
+      <c r="CR52">
+        <v>0</v>
+      </c>
+      <c r="CS52">
+        <v>0</v>
+      </c>
+      <c r="CT52">
+        <v>0</v>
+      </c>
+      <c r="CU52">
+        <v>0</v>
+      </c>
+      <c r="CV52">
+        <v>0</v>
+      </c>
+      <c r="CW52">
+        <v>0</v>
+      </c>
+      <c r="CX52">
+        <v>0</v>
+      </c>
+      <c r="CY52">
+        <v>0</v>
+      </c>
+      <c r="CZ52">
+        <v>0</v>
+      </c>
+      <c r="DA52">
+        <v>0</v>
+      </c>
+      <c r="DB52">
+        <v>0</v>
+      </c>
+      <c r="DC52">
+        <v>0</v>
+      </c>
+      <c r="DD52">
+        <v>0</v>
+      </c>
+      <c r="DE52">
+        <v>0</v>
+      </c>
+      <c r="DF52">
+        <v>0</v>
+      </c>
+      <c r="DG52">
+        <v>0</v>
+      </c>
+      <c r="DH52">
+        <v>0</v>
+      </c>
+      <c r="DI52">
+        <v>0</v>
+      </c>
+      <c r="DJ52">
+        <v>0</v>
+      </c>
+      <c r="DK52">
         <v>0</v>
       </c>
       <c r="DL52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="DN52" t="s">
+        <v>265</v>
+      </c>
+      <c r="DO52" t="s">
+        <v>309</v>
+      </c>
+      <c r="DP52" t="s">
+        <v>297</v>
+      </c>
+      <c r="DQ52" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT52">
+        <v>15.11</v>
+      </c>
+      <c r="DV52">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="DW52">
+        <v>5.3</v>
+      </c>
     </row>
-    <row r="53" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11560,19 +15303,238 @@
       <c r="K53">
         <v>370</v>
       </c>
+      <c r="L53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N53" t="s">
+        <v>89</v>
+      </c>
+      <c r="O53" t="s">
+        <v>88</v>
+      </c>
+      <c r="P53" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>88</v>
+      </c>
+      <c r="R53" t="s">
+        <v>88</v>
+      </c>
+      <c r="S53" t="s">
+        <v>88</v>
+      </c>
+      <c r="T53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W53" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV53">
+        <v>0</v>
+      </c>
+      <c r="AW53">
+        <v>0</v>
+      </c>
+      <c r="AX53">
+        <v>0</v>
+      </c>
+      <c r="AY53">
+        <v>0</v>
+      </c>
+      <c r="AZ53">
+        <v>0</v>
+      </c>
+      <c r="BA53">
+        <v>1</v>
+      </c>
+      <c r="BB53">
+        <v>0</v>
+      </c>
+      <c r="BC53">
+        <v>0</v>
+      </c>
+      <c r="BD53">
+        <v>0</v>
+      </c>
+      <c r="BE53">
+        <v>0</v>
+      </c>
+      <c r="BF53">
+        <v>0</v>
+      </c>
+      <c r="BG53">
+        <v>2</v>
+      </c>
+      <c r="BH53">
+        <v>0</v>
+      </c>
+      <c r="BI53">
+        <v>0</v>
+      </c>
+      <c r="BJ53">
+        <v>0</v>
+      </c>
+      <c r="BK53">
+        <v>0</v>
+      </c>
+      <c r="BL53">
+        <v>0</v>
+      </c>
+      <c r="BM53">
+        <v>0</v>
+      </c>
+      <c r="BN53">
+        <v>1</v>
+      </c>
+      <c r="BO53">
+        <v>0</v>
+      </c>
+      <c r="BP53">
+        <v>0</v>
+      </c>
+      <c r="BQ53">
+        <v>0</v>
+      </c>
+      <c r="BR53">
+        <v>0</v>
+      </c>
+      <c r="BS53">
+        <v>0</v>
+      </c>
+      <c r="BT53">
+        <v>0</v>
+      </c>
+      <c r="BU53">
+        <v>1</v>
+      </c>
+      <c r="BV53">
+        <v>0</v>
+      </c>
+      <c r="BW53">
+        <v>0</v>
+      </c>
+      <c r="BX53">
+        <v>0</v>
+      </c>
+      <c r="BY53">
+        <v>0</v>
+      </c>
+      <c r="BZ53">
+        <v>0</v>
+      </c>
+      <c r="CA53">
+        <v>0</v>
+      </c>
+      <c r="CB53">
+        <v>0</v>
+      </c>
+      <c r="CC53">
+        <v>1</v>
+      </c>
+      <c r="CD53">
+        <v>0</v>
+      </c>
       <c r="CE53">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF53">
+        <v>0</v>
+      </c>
+      <c r="CQ53">
+        <v>0</v>
+      </c>
+      <c r="CR53">
+        <v>0</v>
+      </c>
+      <c r="CS53">
+        <v>0</v>
+      </c>
+      <c r="CT53">
+        <v>1</v>
+      </c>
+      <c r="CU53">
+        <v>0</v>
+      </c>
+      <c r="CV53">
+        <v>0</v>
+      </c>
+      <c r="CW53">
+        <v>0</v>
+      </c>
+      <c r="CX53">
+        <v>0</v>
+      </c>
+      <c r="CY53">
+        <v>0</v>
+      </c>
+      <c r="CZ53">
+        <v>0</v>
+      </c>
+      <c r="DA53">
+        <v>1</v>
+      </c>
+      <c r="DB53">
+        <v>0</v>
+      </c>
+      <c r="DC53">
+        <v>0</v>
+      </c>
+      <c r="DD53">
+        <v>0</v>
+      </c>
+      <c r="DE53">
+        <v>0</v>
+      </c>
+      <c r="DF53">
+        <v>0</v>
+      </c>
+      <c r="DG53">
+        <v>0</v>
+      </c>
+      <c r="DH53">
+        <v>0</v>
+      </c>
+      <c r="DI53">
+        <v>0</v>
+      </c>
+      <c r="DJ53">
+        <v>0</v>
+      </c>
+      <c r="DK53">
         <v>0</v>
       </c>
       <c r="DL53">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="DT53">
+        <v>9.9</v>
+      </c>
+      <c r="DV53">
+        <v>4.7</v>
+      </c>
+      <c r="DW53">
+        <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11606,19 +15568,238 @@
       <c r="K54">
         <v>300</v>
       </c>
+      <c r="L54" t="s">
+        <v>88</v>
+      </c>
+      <c r="M54" t="s">
+        <v>88</v>
+      </c>
+      <c r="N54" t="s">
+        <v>88</v>
+      </c>
+      <c r="O54" t="s">
+        <v>88</v>
+      </c>
+      <c r="P54" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>88</v>
+      </c>
+      <c r="R54" t="s">
+        <v>88</v>
+      </c>
+      <c r="S54" t="s">
+        <v>88</v>
+      </c>
+      <c r="T54" t="s">
+        <v>88</v>
+      </c>
+      <c r="U54" t="s">
+        <v>88</v>
+      </c>
+      <c r="V54" t="s">
+        <v>88</v>
+      </c>
+      <c r="W54" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV54">
+        <v>0</v>
+      </c>
+      <c r="AW54">
+        <v>0</v>
+      </c>
+      <c r="AX54">
+        <v>0</v>
+      </c>
+      <c r="AY54">
+        <v>0</v>
+      </c>
+      <c r="AZ54">
+        <v>0</v>
+      </c>
+      <c r="BA54">
+        <v>1</v>
+      </c>
+      <c r="BB54">
+        <v>0</v>
+      </c>
+      <c r="BC54">
+        <v>0</v>
+      </c>
+      <c r="BD54">
+        <v>0</v>
+      </c>
+      <c r="BE54">
+        <v>0</v>
+      </c>
+      <c r="BF54">
+        <v>0</v>
+      </c>
+      <c r="BG54">
+        <v>0</v>
+      </c>
+      <c r="BH54">
+        <v>2</v>
+      </c>
+      <c r="BI54">
+        <v>0</v>
+      </c>
+      <c r="BJ54">
+        <v>0</v>
+      </c>
+      <c r="BK54">
+        <v>0</v>
+      </c>
+      <c r="BL54">
+        <v>0</v>
+      </c>
+      <c r="BM54">
+        <v>1</v>
+      </c>
+      <c r="BN54">
+        <v>0</v>
+      </c>
+      <c r="BO54">
+        <v>0</v>
+      </c>
+      <c r="BP54">
+        <v>0</v>
+      </c>
+      <c r="BQ54">
+        <v>0</v>
+      </c>
+      <c r="BR54">
+        <v>0</v>
+      </c>
+      <c r="BS54">
+        <v>0</v>
+      </c>
+      <c r="BT54">
+        <v>1</v>
+      </c>
+      <c r="BU54">
+        <v>0</v>
+      </c>
+      <c r="BV54">
+        <v>0</v>
+      </c>
+      <c r="BW54">
+        <v>0</v>
+      </c>
+      <c r="BX54">
+        <v>0</v>
+      </c>
+      <c r="BY54">
+        <v>0</v>
+      </c>
+      <c r="BZ54">
+        <v>0</v>
+      </c>
+      <c r="CA54">
+        <v>0</v>
+      </c>
+      <c r="CB54">
+        <v>1</v>
+      </c>
+      <c r="CC54">
+        <v>0</v>
+      </c>
+      <c r="CD54">
+        <v>0</v>
+      </c>
       <c r="CE54">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF54">
+        <v>0</v>
+      </c>
+      <c r="CQ54">
+        <v>0</v>
+      </c>
+      <c r="CR54">
+        <v>0</v>
+      </c>
+      <c r="CS54">
+        <v>0</v>
+      </c>
+      <c r="CT54">
+        <v>0</v>
+      </c>
+      <c r="CU54">
+        <v>0</v>
+      </c>
+      <c r="CV54">
+        <v>0</v>
+      </c>
+      <c r="CW54">
+        <v>0</v>
+      </c>
+      <c r="CX54">
+        <v>0</v>
+      </c>
+      <c r="CY54">
+        <v>0</v>
+      </c>
+      <c r="CZ54">
+        <v>0</v>
+      </c>
+      <c r="DA54">
+        <v>0</v>
+      </c>
+      <c r="DB54">
+        <v>0</v>
+      </c>
+      <c r="DC54">
+        <v>1</v>
+      </c>
+      <c r="DD54">
+        <v>0</v>
+      </c>
+      <c r="DE54">
+        <v>0</v>
+      </c>
+      <c r="DF54">
+        <v>0</v>
+      </c>
+      <c r="DG54">
+        <v>0</v>
+      </c>
+      <c r="DH54">
+        <v>0</v>
+      </c>
+      <c r="DI54">
+        <v>0</v>
+      </c>
+      <c r="DJ54">
+        <v>0</v>
+      </c>
+      <c r="DK54">
         <v>0</v>
       </c>
       <c r="DL54">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DN54" t="s">
+        <v>276</v>
+      </c>
+      <c r="DO54" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT54">
+        <v>7.95</v>
+      </c>
+      <c r="DV54">
+        <v>5.5</v>
+      </c>
+      <c r="DW54">
+        <v>6.5</v>
       </c>
     </row>
-    <row r="55" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11652,19 +15833,253 @@
       <c r="K55">
         <v>600</v>
       </c>
+      <c r="L55" t="s">
+        <v>88</v>
+      </c>
+      <c r="M55" t="s">
+        <v>88</v>
+      </c>
+      <c r="O55" t="s">
+        <v>88</v>
+      </c>
+      <c r="P55" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>88</v>
+      </c>
+      <c r="R55" t="s">
+        <v>88</v>
+      </c>
+      <c r="S55" t="s">
+        <v>88</v>
+      </c>
+      <c r="T55" t="s">
+        <v>88</v>
+      </c>
+      <c r="U55" t="s">
+        <v>88</v>
+      </c>
+      <c r="V55" t="s">
+        <v>89</v>
+      </c>
+      <c r="W55" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>266</v>
+      </c>
+      <c r="AR55" t="s">
+        <v>226</v>
+      </c>
+      <c r="AS55" t="s">
+        <v>227</v>
+      </c>
+      <c r="AV55">
+        <v>0</v>
+      </c>
+      <c r="AW55">
+        <v>0</v>
+      </c>
+      <c r="AX55">
+        <v>0</v>
+      </c>
+      <c r="AY55">
+        <v>0</v>
+      </c>
+      <c r="AZ55">
+        <v>1</v>
+      </c>
+      <c r="BA55">
+        <v>0</v>
+      </c>
+      <c r="BB55">
+        <v>0</v>
+      </c>
+      <c r="BC55">
+        <v>0</v>
+      </c>
+      <c r="BD55">
+        <v>0</v>
+      </c>
+      <c r="BE55">
+        <v>0</v>
+      </c>
+      <c r="BF55">
+        <v>2</v>
+      </c>
+      <c r="BG55">
+        <v>0</v>
+      </c>
+      <c r="BH55">
+        <v>0</v>
+      </c>
+      <c r="BI55">
+        <v>0</v>
+      </c>
+      <c r="BJ55">
+        <v>0</v>
+      </c>
+      <c r="BK55">
+        <v>0</v>
+      </c>
+      <c r="BL55">
+        <v>0</v>
+      </c>
+      <c r="BM55">
+        <v>1</v>
+      </c>
+      <c r="BN55">
+        <v>0</v>
+      </c>
+      <c r="BO55">
+        <v>0</v>
+      </c>
+      <c r="BP55">
+        <v>0</v>
+      </c>
+      <c r="BQ55">
+        <v>0</v>
+      </c>
+      <c r="BR55">
+        <v>0</v>
+      </c>
+      <c r="BS55">
+        <v>0</v>
+      </c>
+      <c r="BT55">
+        <v>1</v>
+      </c>
+      <c r="BU55">
+        <v>0</v>
+      </c>
+      <c r="BV55">
+        <v>0</v>
+      </c>
+      <c r="BW55">
+        <v>0</v>
+      </c>
+      <c r="BX55">
+        <v>0</v>
+      </c>
+      <c r="BY55">
+        <v>0</v>
+      </c>
+      <c r="BZ55">
+        <v>0</v>
+      </c>
+      <c r="CA55">
+        <v>0</v>
+      </c>
+      <c r="CB55">
+        <v>1</v>
+      </c>
+      <c r="CC55">
+        <v>0</v>
+      </c>
+      <c r="CD55">
+        <v>0</v>
+      </c>
       <c r="CE55">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF55">
+        <v>0</v>
+      </c>
+      <c r="CQ55">
+        <v>0</v>
+      </c>
+      <c r="CR55">
+        <v>0</v>
+      </c>
+      <c r="CS55">
+        <v>0</v>
+      </c>
+      <c r="CT55">
+        <v>0</v>
+      </c>
+      <c r="CU55">
+        <v>0</v>
+      </c>
+      <c r="CV55">
+        <v>0</v>
+      </c>
+      <c r="CW55">
+        <v>0</v>
+      </c>
+      <c r="CX55">
+        <v>0</v>
+      </c>
+      <c r="CY55">
+        <v>0</v>
+      </c>
+      <c r="CZ55">
+        <v>0</v>
+      </c>
+      <c r="DA55">
+        <v>0</v>
+      </c>
+      <c r="DB55">
+        <v>0</v>
+      </c>
+      <c r="DC55">
+        <v>0</v>
+      </c>
+      <c r="DD55">
+        <v>0</v>
+      </c>
+      <c r="DE55">
+        <v>0</v>
+      </c>
+      <c r="DF55">
+        <v>0</v>
+      </c>
+      <c r="DG55">
+        <v>0</v>
+      </c>
+      <c r="DH55">
+        <v>0</v>
+      </c>
+      <c r="DI55">
+        <v>0</v>
+      </c>
+      <c r="DJ55">
+        <v>0</v>
+      </c>
+      <c r="DK55">
         <v>0</v>
       </c>
       <c r="DL55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="DN55" t="s">
+        <v>276</v>
+      </c>
+      <c r="DO55" t="s">
+        <v>266</v>
+      </c>
+      <c r="DP55" t="s">
+        <v>310</v>
+      </c>
+      <c r="DQ55" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT55">
+        <v>12.65</v>
+      </c>
+      <c r="DV55">
+        <v>4.45</v>
+      </c>
+      <c r="DW55">
+        <v>4.45</v>
+      </c>
     </row>
-    <row r="56" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:127" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11698,19 +16113,235 @@
       <c r="K56">
         <v>500</v>
       </c>
+      <c r="L56" t="s">
+        <v>88</v>
+      </c>
+      <c r="M56" t="s">
+        <v>88</v>
+      </c>
+      <c r="N56" t="s">
+        <v>88</v>
+      </c>
+      <c r="O56" t="s">
+        <v>88</v>
+      </c>
+      <c r="P56" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>88</v>
+      </c>
+      <c r="R56" t="s">
+        <v>88</v>
+      </c>
+      <c r="S56" t="s">
+        <v>88</v>
+      </c>
+      <c r="T56" t="s">
+        <v>88</v>
+      </c>
+      <c r="V56" t="s">
+        <v>88</v>
+      </c>
+      <c r="W56" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP56" t="s">
+        <v>226</v>
+      </c>
+      <c r="AQ56" t="s">
+        <v>266</v>
+      </c>
+      <c r="AV56">
+        <v>0</v>
+      </c>
+      <c r="AW56">
+        <v>0</v>
+      </c>
+      <c r="AX56">
+        <v>0</v>
+      </c>
+      <c r="AY56">
+        <v>0</v>
+      </c>
+      <c r="AZ56">
+        <v>0</v>
+      </c>
+      <c r="BA56" s="6">
+        <v>1</v>
+      </c>
+      <c r="BB56" s="6">
+        <v>1</v>
+      </c>
+      <c r="BC56">
+        <v>0</v>
+      </c>
+      <c r="BD56">
+        <v>0</v>
+      </c>
+      <c r="BE56">
+        <v>0</v>
+      </c>
+      <c r="BF56">
+        <v>0</v>
+      </c>
+      <c r="BG56" s="6">
+        <v>4</v>
+      </c>
+      <c r="BH56">
+        <v>0</v>
+      </c>
+      <c r="BI56">
+        <v>0</v>
+      </c>
+      <c r="BJ56">
+        <v>0</v>
+      </c>
+      <c r="BK56">
+        <v>0</v>
+      </c>
+      <c r="BL56">
+        <v>0</v>
+      </c>
+      <c r="BM56">
+        <v>0</v>
+      </c>
+      <c r="BN56">
+        <v>0</v>
+      </c>
+      <c r="BO56">
+        <v>0</v>
+      </c>
+      <c r="BP56">
+        <v>0</v>
+      </c>
+      <c r="BQ56">
+        <v>0</v>
+      </c>
+      <c r="BR56">
+        <v>0</v>
+      </c>
+      <c r="BS56">
+        <v>0</v>
+      </c>
+      <c r="BT56">
+        <v>0</v>
+      </c>
+      <c r="BU56">
+        <v>0</v>
+      </c>
+      <c r="BV56">
+        <v>0</v>
+      </c>
+      <c r="BW56">
+        <v>0</v>
+      </c>
+      <c r="BX56">
+        <v>0</v>
+      </c>
+      <c r="BY56">
+        <v>0</v>
+      </c>
+      <c r="BZ56">
+        <v>0</v>
+      </c>
+      <c r="CA56">
+        <v>0</v>
+      </c>
+      <c r="CB56">
+        <v>0</v>
+      </c>
+      <c r="CC56">
+        <v>0</v>
+      </c>
+      <c r="CD56" s="6">
+        <v>1</v>
+      </c>
       <c r="CE56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CF56">
+        <v>0</v>
+      </c>
+      <c r="CQ56">
+        <v>0</v>
+      </c>
+      <c r="CR56">
+        <v>0</v>
+      </c>
+      <c r="CS56">
+        <v>0</v>
+      </c>
+      <c r="CT56">
+        <v>0</v>
+      </c>
+      <c r="CU56">
+        <v>0</v>
+      </c>
+      <c r="CV56">
+        <v>0</v>
+      </c>
+      <c r="CW56">
+        <v>0</v>
+      </c>
+      <c r="CX56">
+        <v>0</v>
+      </c>
+      <c r="CY56">
+        <v>0</v>
+      </c>
+      <c r="CZ56">
+        <v>0</v>
+      </c>
+      <c r="DA56">
+        <v>0</v>
+      </c>
+      <c r="DB56">
+        <v>0</v>
+      </c>
+      <c r="DC56">
+        <v>0</v>
+      </c>
+      <c r="DD56" s="6">
+        <v>1</v>
+      </c>
+      <c r="DE56">
+        <v>0</v>
+      </c>
+      <c r="DF56">
+        <v>0</v>
+      </c>
+      <c r="DG56">
+        <v>0</v>
+      </c>
+      <c r="DH56">
+        <v>0</v>
+      </c>
+      <c r="DI56">
+        <v>0</v>
+      </c>
+      <c r="DJ56">
+        <v>0</v>
+      </c>
+      <c r="DK56">
         <v>0</v>
       </c>
       <c r="DL56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DT56">
+        <v>9.85</v>
+      </c>
+      <c r="DV56">
+        <v>6.35</v>
+      </c>
+      <c r="DW56">
+        <v>6.65</v>
       </c>
     </row>
-    <row r="57" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11744,19 +16375,244 @@
       <c r="K57">
         <v>615</v>
       </c>
+      <c r="L57" t="s">
+        <v>88</v>
+      </c>
+      <c r="M57" t="s">
+        <v>88</v>
+      </c>
+      <c r="N57" t="s">
+        <v>88</v>
+      </c>
+      <c r="O57" t="s">
+        <v>88</v>
+      </c>
+      <c r="P57" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>88</v>
+      </c>
+      <c r="R57" t="s">
+        <v>88</v>
+      </c>
+      <c r="S57" t="s">
+        <v>89</v>
+      </c>
+      <c r="T57" t="s">
+        <v>88</v>
+      </c>
+      <c r="U57" t="s">
+        <v>89</v>
+      </c>
+      <c r="V57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W57" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>273</v>
+      </c>
+      <c r="AM57" t="s">
+        <v>311</v>
+      </c>
+      <c r="AP57" t="s">
+        <v>225</v>
+      </c>
+      <c r="AQ57" t="s">
+        <v>312</v>
+      </c>
+      <c r="AV57">
+        <v>0</v>
+      </c>
+      <c r="AW57">
+        <v>0</v>
+      </c>
+      <c r="AX57">
+        <v>0</v>
+      </c>
+      <c r="AY57">
+        <v>0</v>
+      </c>
+      <c r="AZ57">
+        <v>0</v>
+      </c>
+      <c r="BA57">
+        <v>0</v>
+      </c>
+      <c r="BB57" s="6">
+        <v>1</v>
+      </c>
+      <c r="BC57">
+        <v>0</v>
+      </c>
+      <c r="BD57">
+        <v>0</v>
+      </c>
+      <c r="BE57">
+        <v>0</v>
+      </c>
+      <c r="BF57">
+        <v>0</v>
+      </c>
+      <c r="BG57">
+        <v>6</v>
+      </c>
+      <c r="BH57">
+        <v>0</v>
+      </c>
+      <c r="BI57">
+        <v>0</v>
+      </c>
+      <c r="BJ57">
+        <v>0</v>
+      </c>
+      <c r="BK57">
+        <v>0</v>
+      </c>
+      <c r="BL57">
+        <v>0</v>
+      </c>
+      <c r="BM57">
+        <v>0</v>
+      </c>
+      <c r="BN57">
+        <v>0</v>
+      </c>
+      <c r="BO57">
+        <v>0</v>
+      </c>
+      <c r="BP57">
+        <v>1</v>
+      </c>
+      <c r="BQ57">
+        <v>0</v>
+      </c>
+      <c r="BR57">
+        <v>0</v>
+      </c>
+      <c r="BS57">
+        <v>0</v>
+      </c>
+      <c r="BT57">
+        <v>0</v>
+      </c>
+      <c r="BU57">
+        <v>0</v>
+      </c>
+      <c r="BV57">
+        <v>0</v>
+      </c>
+      <c r="BW57">
+        <v>1</v>
+      </c>
+      <c r="BX57">
+        <v>0</v>
+      </c>
+      <c r="BY57">
+        <v>0</v>
+      </c>
+      <c r="BZ57">
+        <v>0</v>
+      </c>
+      <c r="CA57">
+        <v>0</v>
+      </c>
+      <c r="CB57">
+        <v>0</v>
+      </c>
+      <c r="CC57">
+        <v>0</v>
+      </c>
+      <c r="CD57">
+        <v>1</v>
+      </c>
       <c r="CE57">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CF57">
+        <v>0</v>
+      </c>
+      <c r="CQ57">
+        <v>0</v>
+      </c>
+      <c r="CR57">
+        <v>0</v>
+      </c>
+      <c r="CS57">
+        <v>0</v>
+      </c>
+      <c r="CT57">
+        <v>0</v>
+      </c>
+      <c r="CU57">
+        <v>0</v>
+      </c>
+      <c r="CV57">
+        <v>0</v>
+      </c>
+      <c r="CW57" s="5">
+        <v>1</v>
+      </c>
+      <c r="CX57">
+        <v>0</v>
+      </c>
+      <c r="CY57">
+        <v>0</v>
+      </c>
+      <c r="CZ57">
+        <v>0</v>
+      </c>
+      <c r="DA57">
+        <v>0</v>
+      </c>
+      <c r="DB57">
+        <v>0</v>
+      </c>
+      <c r="DC57">
+        <v>6</v>
+      </c>
+      <c r="DD57">
+        <v>0</v>
+      </c>
+      <c r="DE57">
+        <v>0</v>
+      </c>
+      <c r="DF57">
+        <v>0</v>
+      </c>
+      <c r="DG57">
+        <v>0</v>
+      </c>
+      <c r="DH57">
+        <v>0</v>
+      </c>
+      <c r="DI57">
+        <v>0</v>
+      </c>
+      <c r="DJ57">
+        <v>0</v>
+      </c>
+      <c r="DK57">
         <v>0</v>
       </c>
       <c r="DL57">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="DT57">
+        <v>14</v>
+      </c>
+      <c r="DV57">
+        <v>3.95</v>
+      </c>
+      <c r="DW57">
+        <v>4.25</v>
       </c>
     </row>
-    <row r="58" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11790,19 +16646,243 @@
       <c r="K58">
         <v>600</v>
       </c>
+      <c r="L58" t="s">
+        <v>88</v>
+      </c>
+      <c r="M58" t="s">
+        <v>88</v>
+      </c>
+      <c r="N58" t="s">
+        <v>88</v>
+      </c>
+      <c r="O58" t="s">
+        <v>88</v>
+      </c>
+      <c r="P58" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>88</v>
+      </c>
+      <c r="R58" t="s">
+        <v>88</v>
+      </c>
+      <c r="S58" t="s">
+        <v>88</v>
+      </c>
+      <c r="T58" t="s">
+        <v>88</v>
+      </c>
+      <c r="U58" t="s">
+        <v>88</v>
+      </c>
+      <c r="V58" t="s">
+        <v>88</v>
+      </c>
+      <c r="W58" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>274</v>
+      </c>
+      <c r="AV58">
+        <v>0</v>
+      </c>
+      <c r="AW58">
+        <v>0</v>
+      </c>
+      <c r="AX58">
+        <v>0</v>
+      </c>
+      <c r="AY58">
+        <v>1</v>
+      </c>
+      <c r="AZ58">
+        <v>0</v>
+      </c>
+      <c r="BA58">
+        <v>0</v>
+      </c>
+      <c r="BB58">
+        <v>0</v>
+      </c>
+      <c r="BC58">
+        <v>0</v>
+      </c>
+      <c r="BD58">
+        <v>0</v>
+      </c>
+      <c r="BE58">
+        <v>0</v>
+      </c>
+      <c r="BF58">
+        <v>0</v>
+      </c>
+      <c r="BG58">
+        <v>0</v>
+      </c>
+      <c r="BH58">
+        <v>0</v>
+      </c>
+      <c r="BI58">
+        <v>0</v>
+      </c>
+      <c r="BJ58">
+        <v>0</v>
+      </c>
+      <c r="BK58">
+        <v>0</v>
+      </c>
+      <c r="BL58">
+        <v>0</v>
+      </c>
+      <c r="BM58">
+        <v>0</v>
+      </c>
+      <c r="BN58">
+        <v>1</v>
+      </c>
+      <c r="BO58">
+        <v>0</v>
+      </c>
+      <c r="BP58">
+        <v>0</v>
+      </c>
+      <c r="BQ58">
+        <v>0</v>
+      </c>
+      <c r="BR58">
+        <v>0</v>
+      </c>
+      <c r="BS58">
+        <v>0</v>
+      </c>
+      <c r="BT58">
+        <v>1</v>
+      </c>
+      <c r="BU58">
+        <v>0</v>
+      </c>
+      <c r="BV58">
+        <v>0</v>
+      </c>
+      <c r="BW58">
+        <v>0</v>
+      </c>
+      <c r="BX58">
+        <v>0</v>
+      </c>
+      <c r="BY58">
+        <v>0</v>
+      </c>
+      <c r="BZ58">
+        <v>0</v>
+      </c>
+      <c r="CA58">
+        <v>0</v>
+      </c>
+      <c r="CB58">
+        <v>1</v>
+      </c>
+      <c r="CC58">
+        <v>0</v>
+      </c>
+      <c r="CD58">
+        <v>0</v>
+      </c>
       <c r="CE58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CF58">
         <v>0</v>
       </c>
+      <c r="CQ58">
+        <v>0</v>
+      </c>
+      <c r="CR58">
+        <v>0</v>
+      </c>
+      <c r="CS58">
+        <v>0</v>
+      </c>
+      <c r="CT58">
+        <v>0</v>
+      </c>
+      <c r="CU58">
+        <v>0</v>
+      </c>
+      <c r="CV58">
+        <v>0</v>
+      </c>
+      <c r="CW58">
+        <v>0</v>
+      </c>
+      <c r="CX58">
+        <v>0</v>
+      </c>
+      <c r="CY58">
+        <v>0</v>
+      </c>
+      <c r="CZ58">
+        <v>0</v>
+      </c>
+      <c r="DA58">
+        <v>0</v>
+      </c>
+      <c r="DB58">
+        <v>0</v>
+      </c>
+      <c r="DC58">
+        <v>0</v>
+      </c>
+      <c r="DD58">
+        <v>0</v>
+      </c>
+      <c r="DE58">
+        <v>0</v>
+      </c>
+      <c r="DF58">
+        <v>0</v>
+      </c>
+      <c r="DG58">
+        <v>0</v>
+      </c>
+      <c r="DH58">
+        <v>0</v>
+      </c>
+      <c r="DI58">
+        <v>0</v>
+      </c>
+      <c r="DJ58">
+        <v>0</v>
+      </c>
+      <c r="DK58">
+        <v>0</v>
+      </c>
       <c r="DL58">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="DN58" t="s">
+        <v>283</v>
+      </c>
+      <c r="DO58" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT58">
+        <v>11.9</v>
+      </c>
+      <c r="DV58">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DW58">
+        <v>4.5</v>
       </c>
     </row>
-    <row r="59" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11836,19 +16916,238 @@
       <c r="K59">
         <v>600</v>
       </c>
+      <c r="L59" t="s">
+        <v>88</v>
+      </c>
+      <c r="M59" t="s">
+        <v>88</v>
+      </c>
+      <c r="N59" t="s">
+        <v>88</v>
+      </c>
+      <c r="O59" t="s">
+        <v>88</v>
+      </c>
+      <c r="P59" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>88</v>
+      </c>
+      <c r="R59" t="s">
+        <v>88</v>
+      </c>
+      <c r="S59" t="s">
+        <v>88</v>
+      </c>
+      <c r="T59" t="s">
+        <v>88</v>
+      </c>
+      <c r="U59" t="s">
+        <v>88</v>
+      </c>
+      <c r="V59" t="s">
+        <v>88</v>
+      </c>
+      <c r="W59" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV59">
+        <v>0</v>
+      </c>
+      <c r="AW59">
+        <v>0</v>
+      </c>
+      <c r="AX59">
+        <v>0</v>
+      </c>
+      <c r="AY59">
+        <v>0</v>
+      </c>
+      <c r="AZ59">
+        <v>0</v>
+      </c>
+      <c r="BA59">
+        <v>1</v>
+      </c>
+      <c r="BB59">
+        <v>0</v>
+      </c>
+      <c r="BC59">
+        <v>2</v>
+      </c>
+      <c r="BD59">
+        <v>0</v>
+      </c>
+      <c r="BE59">
+        <v>0</v>
+      </c>
+      <c r="BF59">
+        <v>0</v>
+      </c>
+      <c r="BG59">
+        <v>0</v>
+      </c>
+      <c r="BH59">
+        <v>0</v>
+      </c>
+      <c r="BI59">
+        <v>0</v>
+      </c>
+      <c r="BJ59">
+        <v>0</v>
+      </c>
+      <c r="BK59">
+        <v>0</v>
+      </c>
+      <c r="BL59">
+        <v>0</v>
+      </c>
+      <c r="BM59">
+        <v>0</v>
+      </c>
+      <c r="BN59">
+        <v>1</v>
+      </c>
+      <c r="BO59">
+        <v>0</v>
+      </c>
+      <c r="BP59">
+        <v>0</v>
+      </c>
+      <c r="BQ59">
+        <v>0</v>
+      </c>
+      <c r="BR59">
+        <v>0</v>
+      </c>
+      <c r="BS59">
+        <v>0</v>
+      </c>
+      <c r="BT59">
+        <v>0</v>
+      </c>
+      <c r="BU59">
+        <v>1</v>
+      </c>
+      <c r="BV59">
+        <v>0</v>
+      </c>
+      <c r="BW59">
+        <v>0</v>
+      </c>
+      <c r="BX59">
+        <v>0</v>
+      </c>
+      <c r="BY59">
+        <v>0</v>
+      </c>
+      <c r="BZ59">
+        <v>0</v>
+      </c>
+      <c r="CA59">
+        <v>0</v>
+      </c>
+      <c r="CB59">
+        <v>1</v>
+      </c>
+      <c r="CC59">
+        <v>0</v>
+      </c>
+      <c r="CD59">
+        <v>0</v>
+      </c>
       <c r="CE59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF59">
+        <v>0</v>
+      </c>
+      <c r="CQ59">
+        <v>0</v>
+      </c>
+      <c r="CR59">
+        <v>0</v>
+      </c>
+      <c r="CS59">
+        <v>0</v>
+      </c>
+      <c r="CT59">
+        <v>0</v>
+      </c>
+      <c r="CU59">
+        <v>1</v>
+      </c>
+      <c r="CV59">
+        <v>0</v>
+      </c>
+      <c r="CW59">
+        <v>0</v>
+      </c>
+      <c r="CX59">
+        <v>0</v>
+      </c>
+      <c r="CY59">
+        <v>0</v>
+      </c>
+      <c r="CZ59">
+        <v>0</v>
+      </c>
+      <c r="DA59">
+        <v>0</v>
+      </c>
+      <c r="DB59">
+        <v>0</v>
+      </c>
+      <c r="DC59">
+        <v>0</v>
+      </c>
+      <c r="DD59">
+        <v>0</v>
+      </c>
+      <c r="DE59">
+        <v>0</v>
+      </c>
+      <c r="DF59">
+        <v>0</v>
+      </c>
+      <c r="DG59">
+        <v>0</v>
+      </c>
+      <c r="DH59">
+        <v>0</v>
+      </c>
+      <c r="DI59">
+        <v>0</v>
+      </c>
+      <c r="DJ59">
+        <v>0</v>
+      </c>
+      <c r="DK59">
         <v>0</v>
       </c>
       <c r="DL59">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DP59" t="s">
+        <v>226</v>
+      </c>
+      <c r="DQ59" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT59">
+        <v>7.95</v>
+      </c>
+      <c r="DV59">
+        <v>6</v>
+      </c>
+      <c r="DW59">
+        <v>6.4</v>
       </c>
     </row>
-    <row r="60" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -11882,19 +17181,238 @@
       <c r="K60">
         <v>600</v>
       </c>
+      <c r="L60" t="s">
+        <v>88</v>
+      </c>
+      <c r="M60" t="s">
+        <v>88</v>
+      </c>
+      <c r="N60" t="s">
+        <v>89</v>
+      </c>
+      <c r="O60" t="s">
+        <v>88</v>
+      </c>
+      <c r="P60" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>88</v>
+      </c>
+      <c r="R60" t="s">
+        <v>88</v>
+      </c>
+      <c r="S60" t="s">
+        <v>88</v>
+      </c>
+      <c r="T60" t="s">
+        <v>88</v>
+      </c>
+      <c r="U60" t="s">
+        <v>88</v>
+      </c>
+      <c r="V60" t="s">
+        <v>88</v>
+      </c>
+      <c r="W60" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV60">
+        <v>0</v>
+      </c>
+      <c r="AW60">
+        <v>0</v>
+      </c>
+      <c r="AX60">
+        <v>0</v>
+      </c>
+      <c r="AY60">
+        <v>1</v>
+      </c>
+      <c r="AZ60">
+        <v>0</v>
+      </c>
+      <c r="BA60">
+        <v>0</v>
+      </c>
+      <c r="BB60">
+        <v>0</v>
+      </c>
+      <c r="BC60">
+        <v>0</v>
+      </c>
+      <c r="BD60">
+        <v>0</v>
+      </c>
+      <c r="BE60">
+        <v>0</v>
+      </c>
+      <c r="BF60">
+        <v>2</v>
+      </c>
+      <c r="BG60">
+        <v>0</v>
+      </c>
+      <c r="BH60">
+        <v>0</v>
+      </c>
+      <c r="BI60">
+        <v>0</v>
+      </c>
+      <c r="BJ60">
+        <v>0</v>
+      </c>
+      <c r="BK60">
+        <v>0</v>
+      </c>
+      <c r="BL60">
+        <v>0</v>
+      </c>
+      <c r="BM60">
+        <v>1</v>
+      </c>
+      <c r="BN60">
+        <v>0</v>
+      </c>
+      <c r="BO60">
+        <v>0</v>
+      </c>
+      <c r="BP60">
+        <v>0</v>
+      </c>
+      <c r="BQ60">
+        <v>0</v>
+      </c>
+      <c r="BR60">
+        <v>0</v>
+      </c>
+      <c r="BS60">
+        <v>0</v>
+      </c>
+      <c r="BT60">
+        <v>1</v>
+      </c>
+      <c r="BU60">
+        <v>0</v>
+      </c>
+      <c r="BV60">
+        <v>0</v>
+      </c>
+      <c r="BW60">
+        <v>0</v>
+      </c>
+      <c r="BX60">
+        <v>0</v>
+      </c>
+      <c r="BY60">
+        <v>0</v>
+      </c>
+      <c r="BZ60">
+        <v>0</v>
+      </c>
+      <c r="CA60">
+        <v>0</v>
+      </c>
+      <c r="CB60">
+        <v>1</v>
+      </c>
+      <c r="CC60">
+        <v>0</v>
+      </c>
+      <c r="CD60">
+        <v>0</v>
+      </c>
       <c r="CE60">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF60">
+        <v>0</v>
+      </c>
+      <c r="CQ60">
+        <v>0</v>
+      </c>
+      <c r="CR60">
+        <v>0</v>
+      </c>
+      <c r="CS60">
+        <v>0</v>
+      </c>
+      <c r="CT60">
+        <v>1</v>
+      </c>
+      <c r="CU60">
+        <v>0</v>
+      </c>
+      <c r="CV60">
+        <v>0</v>
+      </c>
+      <c r="CW60">
+        <v>0</v>
+      </c>
+      <c r="CX60">
+        <v>0</v>
+      </c>
+      <c r="CY60">
+        <v>0</v>
+      </c>
+      <c r="CZ60">
+        <v>0</v>
+      </c>
+      <c r="DA60">
+        <v>1</v>
+      </c>
+      <c r="DB60">
+        <v>0</v>
+      </c>
+      <c r="DC60">
+        <v>0</v>
+      </c>
+      <c r="DD60">
+        <v>0</v>
+      </c>
+      <c r="DE60">
+        <v>0</v>
+      </c>
+      <c r="DF60">
+        <v>0</v>
+      </c>
+      <c r="DG60">
+        <v>0</v>
+      </c>
+      <c r="DH60">
+        <v>0</v>
+      </c>
+      <c r="DI60">
+        <v>0</v>
+      </c>
+      <c r="DJ60">
+        <v>0</v>
+      </c>
+      <c r="DK60">
         <v>0</v>
       </c>
       <c r="DL60">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="DT60">
+        <v>7.91</v>
+      </c>
+      <c r="DV60">
+        <v>4</v>
+      </c>
+      <c r="DW60">
+        <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -11928,19 +17446,241 @@
       <c r="K61">
         <v>700</v>
       </c>
+      <c r="L61" t="s">
+        <v>88</v>
+      </c>
+      <c r="M61" t="s">
+        <v>88</v>
+      </c>
+      <c r="O61" t="s">
+        <v>88</v>
+      </c>
+      <c r="P61" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>88</v>
+      </c>
+      <c r="R61" t="s">
+        <v>88</v>
+      </c>
+      <c r="S61" t="s">
+        <v>88</v>
+      </c>
+      <c r="T61" t="s">
+        <v>88</v>
+      </c>
+      <c r="U61" t="s">
+        <v>88</v>
+      </c>
+      <c r="V61" t="s">
+        <v>88</v>
+      </c>
+      <c r="W61" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>266</v>
+      </c>
+      <c r="AV61">
+        <v>0</v>
+      </c>
+      <c r="AW61">
+        <v>0</v>
+      </c>
+      <c r="AX61">
+        <v>0</v>
+      </c>
+      <c r="AY61">
+        <v>0</v>
+      </c>
+      <c r="AZ61">
+        <v>0</v>
+      </c>
+      <c r="BA61">
+        <v>0</v>
+      </c>
+      <c r="BB61">
+        <v>1</v>
+      </c>
+      <c r="BC61">
+        <v>0</v>
+      </c>
+      <c r="BD61">
+        <v>0</v>
+      </c>
+      <c r="BE61">
+        <v>0</v>
+      </c>
+      <c r="BF61">
+        <v>2</v>
+      </c>
+      <c r="BG61">
+        <v>0</v>
+      </c>
+      <c r="BH61">
+        <v>0</v>
+      </c>
+      <c r="BI61">
+        <v>0</v>
+      </c>
+      <c r="BJ61">
+        <v>0</v>
+      </c>
+      <c r="BK61">
+        <v>0</v>
+      </c>
+      <c r="BL61">
+        <v>0</v>
+      </c>
+      <c r="BM61">
+        <v>0</v>
+      </c>
+      <c r="BN61">
+        <v>0</v>
+      </c>
+      <c r="BO61">
+        <v>1</v>
+      </c>
+      <c r="BP61">
+        <v>0</v>
+      </c>
+      <c r="BQ61">
+        <v>0</v>
+      </c>
+      <c r="BR61">
+        <v>0</v>
+      </c>
+      <c r="BS61">
+        <v>0</v>
+      </c>
+      <c r="BT61">
+        <v>0</v>
+      </c>
+      <c r="BU61">
+        <v>0</v>
+      </c>
+      <c r="BV61">
+        <v>1</v>
+      </c>
+      <c r="BW61">
+        <v>0</v>
+      </c>
+      <c r="BX61">
+        <v>0</v>
+      </c>
+      <c r="BY61">
+        <v>0</v>
+      </c>
+      <c r="BZ61">
+        <v>0</v>
+      </c>
+      <c r="CA61">
+        <v>0</v>
+      </c>
+      <c r="CB61">
+        <v>0</v>
+      </c>
+      <c r="CC61">
+        <v>0</v>
+      </c>
+      <c r="CD61">
+        <v>1</v>
+      </c>
       <c r="CE61">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF61">
+        <v>0</v>
+      </c>
+      <c r="CQ61">
+        <v>0</v>
+      </c>
+      <c r="CR61">
+        <v>0</v>
+      </c>
+      <c r="CS61">
+        <v>0</v>
+      </c>
+      <c r="CT61">
+        <v>0</v>
+      </c>
+      <c r="CU61">
+        <v>0</v>
+      </c>
+      <c r="CV61">
+        <v>1</v>
+      </c>
+      <c r="CW61">
+        <v>0</v>
+      </c>
+      <c r="CX61">
+        <v>0</v>
+      </c>
+      <c r="CY61">
+        <v>0</v>
+      </c>
+      <c r="CZ61">
+        <v>0</v>
+      </c>
+      <c r="DA61">
+        <v>0</v>
+      </c>
+      <c r="DB61">
+        <v>0</v>
+      </c>
+      <c r="DC61">
+        <v>1</v>
+      </c>
+      <c r="DD61">
+        <v>0</v>
+      </c>
+      <c r="DE61">
+        <v>0</v>
+      </c>
+      <c r="DF61">
+        <v>0</v>
+      </c>
+      <c r="DG61">
+        <v>0</v>
+      </c>
+      <c r="DH61">
+        <v>0</v>
+      </c>
+      <c r="DI61">
+        <v>0</v>
+      </c>
+      <c r="DJ61">
+        <v>0</v>
+      </c>
+      <c r="DK61">
         <v>0</v>
       </c>
       <c r="DL61">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="DP61" t="s">
+        <v>313</v>
+      </c>
+      <c r="DQ61" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT61">
+        <v>12.75</v>
+      </c>
+      <c r="DV61">
+        <v>5.55</v>
+      </c>
+      <c r="DW61">
+        <v>6.1</v>
       </c>
     </row>
-    <row r="62" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -11974,19 +17714,235 @@
       <c r="K62">
         <v>1000</v>
       </c>
+      <c r="L62" t="s">
+        <v>88</v>
+      </c>
+      <c r="M62" t="s">
+        <v>88</v>
+      </c>
+      <c r="O62" t="s">
+        <v>88</v>
+      </c>
+      <c r="P62" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>88</v>
+      </c>
+      <c r="R62" t="s">
+        <v>88</v>
+      </c>
+      <c r="S62" t="s">
+        <v>88</v>
+      </c>
+      <c r="T62" t="s">
+        <v>88</v>
+      </c>
+      <c r="U62" t="s">
+        <v>88</v>
+      </c>
+      <c r="V62" t="s">
+        <v>88</v>
+      </c>
+      <c r="W62" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>266</v>
+      </c>
+      <c r="AV62">
+        <v>0</v>
+      </c>
+      <c r="AW62">
+        <v>0</v>
+      </c>
+      <c r="AX62">
+        <v>0</v>
+      </c>
+      <c r="AY62">
+        <v>0</v>
+      </c>
+      <c r="AZ62">
+        <v>0</v>
+      </c>
+      <c r="BA62">
+        <v>1</v>
+      </c>
+      <c r="BB62">
+        <v>0</v>
+      </c>
+      <c r="BC62">
+        <v>0</v>
+      </c>
+      <c r="BD62">
+        <v>0</v>
+      </c>
+      <c r="BE62">
+        <v>0</v>
+      </c>
+      <c r="BF62">
+        <v>0</v>
+      </c>
+      <c r="BG62">
+        <v>0</v>
+      </c>
+      <c r="BH62">
+        <v>0</v>
+      </c>
+      <c r="BI62">
+        <v>0</v>
+      </c>
+      <c r="BJ62">
+        <v>0</v>
+      </c>
+      <c r="BK62">
+        <v>0</v>
+      </c>
+      <c r="BL62">
+        <v>0</v>
+      </c>
+      <c r="BM62">
+        <v>0</v>
+      </c>
+      <c r="BN62">
+        <v>0</v>
+      </c>
+      <c r="BO62">
+        <v>1</v>
+      </c>
+      <c r="BP62">
+        <v>0</v>
+      </c>
+      <c r="BQ62">
+        <v>0</v>
+      </c>
+      <c r="BR62">
+        <v>0</v>
+      </c>
+      <c r="BS62">
+        <v>0</v>
+      </c>
+      <c r="BT62">
+        <v>0</v>
+      </c>
+      <c r="BU62">
+        <v>0</v>
+      </c>
+      <c r="BV62">
+        <v>1</v>
+      </c>
+      <c r="BW62">
+        <v>0</v>
+      </c>
+      <c r="BX62">
+        <v>0</v>
+      </c>
+      <c r="BY62">
+        <v>0</v>
+      </c>
+      <c r="BZ62">
+        <v>0</v>
+      </c>
+      <c r="CA62">
+        <v>0</v>
+      </c>
+      <c r="CB62">
+        <v>0</v>
+      </c>
+      <c r="CC62">
+        <v>1</v>
+      </c>
+      <c r="CD62">
+        <v>0</v>
+      </c>
       <c r="CE62">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CF62">
+        <v>0</v>
+      </c>
+      <c r="CQ62">
+        <v>0</v>
+      </c>
+      <c r="CR62">
+        <v>0</v>
+      </c>
+      <c r="CS62">
+        <v>0</v>
+      </c>
+      <c r="CT62">
+        <v>0</v>
+      </c>
+      <c r="CU62">
+        <v>0</v>
+      </c>
+      <c r="CV62">
+        <v>1</v>
+      </c>
+      <c r="CW62">
+        <v>0</v>
+      </c>
+      <c r="CX62">
+        <v>0</v>
+      </c>
+      <c r="CY62">
+        <v>0</v>
+      </c>
+      <c r="CZ62">
+        <v>0</v>
+      </c>
+      <c r="DA62">
+        <v>0</v>
+      </c>
+      <c r="DB62">
+        <v>0</v>
+      </c>
+      <c r="DC62">
+        <v>0</v>
+      </c>
+      <c r="DD62">
+        <v>0</v>
+      </c>
+      <c r="DE62">
+        <v>0</v>
+      </c>
+      <c r="DF62">
+        <v>0</v>
+      </c>
+      <c r="DG62">
+        <v>0</v>
+      </c>
+      <c r="DH62">
+        <v>0</v>
+      </c>
+      <c r="DI62">
+        <v>0</v>
+      </c>
+      <c r="DJ62">
+        <v>0</v>
+      </c>
+      <c r="DK62">
         <v>0</v>
       </c>
       <c r="DL62">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DT62">
+        <v>11.4</v>
+      </c>
+      <c r="DV62">
+        <v>4</v>
+      </c>
+      <c r="DW62">
+        <v>3.3</v>
       </c>
     </row>
-    <row r="63" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -12020,16 +17976,259 @@
       <c r="K63">
         <v>650</v>
       </c>
+      <c r="L63" t="s">
+        <v>88</v>
+      </c>
+      <c r="M63" t="s">
+        <v>88</v>
+      </c>
+      <c r="N63" t="s">
+        <v>88</v>
+      </c>
+      <c r="O63" t="s">
+        <v>88</v>
+      </c>
+      <c r="P63" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>88</v>
+      </c>
+      <c r="R63" t="s">
+        <v>88</v>
+      </c>
+      <c r="S63" t="s">
+        <v>89</v>
+      </c>
+      <c r="T63" t="s">
+        <v>88</v>
+      </c>
+      <c r="U63" t="s">
+        <v>89</v>
+      </c>
+      <c r="V63" t="s">
+        <v>88</v>
+      </c>
+      <c r="W63" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>273</v>
+      </c>
+      <c r="AM63" t="s">
+        <v>274</v>
+      </c>
+      <c r="AP63" t="s">
+        <v>275</v>
+      </c>
+      <c r="AQ63" t="s">
+        <v>274</v>
+      </c>
+      <c r="AT63" t="s">
+        <v>314</v>
+      </c>
+      <c r="AU63" t="s">
+        <v>282</v>
+      </c>
+      <c r="AV63">
+        <v>0</v>
+      </c>
+      <c r="AW63">
+        <v>0</v>
+      </c>
+      <c r="AX63">
+        <v>0</v>
+      </c>
+      <c r="AY63">
+        <v>0</v>
+      </c>
+      <c r="AZ63">
+        <v>1</v>
+      </c>
+      <c r="BA63">
+        <v>0</v>
+      </c>
+      <c r="BB63">
+        <v>0</v>
+      </c>
+      <c r="BC63">
+        <v>0</v>
+      </c>
+      <c r="BD63">
+        <v>2</v>
+      </c>
+      <c r="BE63">
+        <v>0</v>
+      </c>
+      <c r="BF63">
+        <v>0</v>
+      </c>
+      <c r="BG63">
+        <v>0</v>
+      </c>
+      <c r="BH63">
+        <v>0</v>
+      </c>
+      <c r="BI63">
+        <v>0</v>
+      </c>
+      <c r="BJ63">
+        <v>0</v>
+      </c>
+      <c r="BK63">
+        <v>0</v>
+      </c>
+      <c r="BL63">
+        <v>0</v>
+      </c>
+      <c r="BM63">
+        <v>0</v>
+      </c>
+      <c r="BN63">
+        <v>1</v>
+      </c>
+      <c r="BO63">
+        <v>0</v>
+      </c>
+      <c r="BP63">
+        <v>0</v>
+      </c>
+      <c r="BQ63">
+        <v>0</v>
+      </c>
+      <c r="BR63">
+        <v>0</v>
+      </c>
+      <c r="BS63">
+        <v>0</v>
+      </c>
+      <c r="BT63">
+        <v>0</v>
+      </c>
+      <c r="BU63">
+        <v>1</v>
+      </c>
+      <c r="BV63">
+        <v>0</v>
+      </c>
+      <c r="BW63">
+        <v>0</v>
+      </c>
+      <c r="BX63">
+        <v>0</v>
+      </c>
+      <c r="BY63">
+        <v>0</v>
+      </c>
+      <c r="BZ63">
+        <v>0</v>
+      </c>
+      <c r="CA63">
+        <v>0</v>
+      </c>
+      <c r="CB63">
+        <v>1</v>
+      </c>
+      <c r="CC63">
+        <v>0</v>
+      </c>
+      <c r="CD63">
+        <v>0</v>
+      </c>
       <c r="CE63">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CF63">
+        <v>0</v>
+      </c>
+      <c r="CQ63">
+        <v>0</v>
+      </c>
+      <c r="CR63">
+        <v>0</v>
+      </c>
+      <c r="CS63">
+        <v>0</v>
+      </c>
+      <c r="CT63">
+        <v>0</v>
+      </c>
+      <c r="CU63">
+        <v>0</v>
+      </c>
+      <c r="CV63">
+        <v>0</v>
+      </c>
+      <c r="CW63">
+        <v>0</v>
+      </c>
+      <c r="CX63">
+        <v>0</v>
+      </c>
+      <c r="CY63">
+        <v>0</v>
+      </c>
+      <c r="CZ63">
+        <v>0</v>
+      </c>
+      <c r="DA63">
+        <v>0</v>
+      </c>
+      <c r="DB63">
+        <v>0</v>
+      </c>
+      <c r="DC63">
+        <v>0</v>
+      </c>
+      <c r="DD63">
+        <v>0</v>
+      </c>
+      <c r="DE63">
+        <v>0</v>
+      </c>
+      <c r="DF63">
+        <v>0</v>
+      </c>
+      <c r="DG63">
+        <v>0</v>
+      </c>
+      <c r="DH63">
+        <v>0</v>
+      </c>
+      <c r="DI63">
+        <v>0</v>
+      </c>
+      <c r="DJ63">
+        <v>0</v>
+      </c>
+      <c r="DK63">
         <v>0</v>
       </c>
       <c r="DL63">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="DN63" t="s">
+        <v>283</v>
+      </c>
+      <c r="DO63" t="s">
+        <v>266</v>
+      </c>
+      <c r="DP63" t="s">
+        <v>277</v>
+      </c>
+      <c r="DQ63" t="s">
+        <v>266</v>
+      </c>
+      <c r="DT63">
+        <v>14.9</v>
+      </c>
+      <c r="DV63">
+        <v>3.8</v>
+      </c>
+      <c r="DW63">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
